--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="121">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -40,24 +40,90 @@
     <t xml:space="preserve">Descricao   </t>
   </si>
   <si>
+    <t>020102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600040      </t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>000125647</t>
+  </si>
+  <si>
+    <t>SD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATALISADOR VIPAL VIPAFIX                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600207      </t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REMOVEDOR QUIMICO VULCAFLEX                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072600061      </t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLA VIPAL VIPAFIX 1KG                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020605696      </t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>000057934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROLETE INFERIOR KOMATSU 131-30                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010500087      </t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>000305501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAXA GADUS S3 V220 C 18KG                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010700061      </t>
+  </si>
+  <si>
+    <t>000305500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO SPIRAX S4 TXM FR 20LT                        </t>
+  </si>
+  <si>
     <t>020202</t>
   </si>
   <si>
     <t xml:space="preserve">020608211      </t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
     <t>000009327</t>
   </si>
   <si>
-    <t>SD1</t>
-  </si>
-  <si>
     <t xml:space="preserve">VALVULA STEINERT STP20 00011/                     </t>
   </si>
   <si>
@@ -76,9 +142,6 @@
     <t xml:space="preserve">040400159      </t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t xml:space="preserve">VASSOURA  V-9 CONDOR UN                           </t>
   </si>
   <si>
@@ -106,12 +169,45 @@
     <t xml:space="preserve">040801159      </t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t xml:space="preserve">SACO P/ LIXO 60LTS PRETO                          </t>
   </si>
   <si>
+    <t xml:space="preserve">020800389      </t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>000010333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO SANDVIK SAHF 9524                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">180200042      </t>
+  </si>
+  <si>
+    <t>000077452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO DE OLEO CHICAGO PNEUMATIC - 2903752600     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020800424      </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO ATLASCOPCO 1613950300 ORIGINAL             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010500285      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLUIDO CHICAGO REFR CP46 19 LT - 1031401261       </t>
+  </si>
+  <si>
     <t>100106</t>
   </si>
   <si>
@@ -127,18 +223,12 @@
     <t xml:space="preserve">040800141      </t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t xml:space="preserve">COXIM AXOR4144/MR420G/MB420G                      </t>
   </si>
   <si>
     <t xml:space="preserve">040201542      </t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 MOLA TRAS AXOX4144 MRB16203                     </t>
   </si>
   <si>
@@ -151,9 +241,6 @@
     <t xml:space="preserve">040201567      </t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t xml:space="preserve">BUCHA  A0003237985/R3375                          </t>
   </si>
   <si>
@@ -178,12 +265,84 @@
     <t xml:space="preserve">040201541      </t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 MOLA TRAS AXOX4144 MRB16202                     </t>
   </si>
   <si>
+    <t xml:space="preserve">040800146      </t>
+  </si>
+  <si>
+    <t>000009566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENTE CAT 597-6033 COMPLETO (COM TRAVA INCLUSA)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300114      </t>
+  </si>
+  <si>
+    <t>000849060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 439-5037                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200662      </t>
+  </si>
+  <si>
+    <t>000062448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CILINDRO MERCEDES A0032607463                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201933      </t>
+  </si>
+  <si>
+    <t>000062442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA MERCEDES A0001405339                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201934      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIDADE MERCEDES A0001407878                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201566      </t>
+  </si>
+  <si>
+    <t>000062441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COXIM MERCEDES A9582411213                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201509      </t>
+  </si>
+  <si>
+    <t>000062449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLIA MERCEDES A0005501933                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040202233      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERRUPTOR COMANDO MERCEDES A0055453413          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">030200001      </t>
+  </si>
+  <si>
+    <t>000125658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTETOR ARO R24 FURO CENTRAL                     </t>
+  </si>
+  <si>
     <t xml:space="preserve">030100012      </t>
   </si>
   <si>
@@ -194,6 +353,27 @@
   </si>
   <si>
     <t xml:space="preserve">PNEU 325/95R24                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300110      </t>
+  </si>
+  <si>
+    <t>000849089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 273-5711                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300117      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 500-0483                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300118      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 523-4987                               </t>
   </si>
 </sst>
 </file>
@@ -591,18 +771,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16.78" customWidth="1"/>
-    <col min="2" max="2" width="21.34" customWidth="1"/>
-    <col min="3" max="3" width="23.34" customWidth="1"/>
-    <col min="4" max="4" width="27.79" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="26.45" customWidth="1"/>
-    <col min="7" max="7" width="19.78" customWidth="1"/>
-    <col min="8" max="8" width="27.79" customWidth="1"/>
-    <col min="9" max="9" width="70.83" customWidth="1"/>
+    <col min="1" max="1" width="11.69" customWidth="1"/>
+    <col min="2" max="2" width="15.3" customWidth="1"/>
+    <col min="3" max="3" width="16.73" customWidth="1"/>
+    <col min="4" max="4" width="19.54" customWidth="1"/>
+    <col min="5" max="5" width="12.76" customWidth="1"/>
+    <col min="6" max="6" width="18.92" customWidth="1"/>
+    <col min="7" max="7" width="13.53" customWidth="1"/>
+    <col min="8" max="8" width="19.77" customWidth="1"/>
+    <col min="9" max="9" width="54.73" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -654,7 +834,7 @@
         <v>13</v>
       </c>
       <c r="G2" s="4">
-        <v>46276.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>14</v>
@@ -680,16 +860,16 @@
         <v>17</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="G3" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -697,28 +877,28 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -726,28 +906,28 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="E5" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G5" s="4">
-        <v>46300.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -755,28 +935,28 @@
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G6" s="4">
-        <v>46300.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -784,57 +964,57 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="G7" s="4">
-        <v>46300.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="G8" s="4">
-        <v>46300.5</v>
+        <v>46276.5</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -842,19 +1022,19 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G9" s="4">
         <v>46300.5</v>
@@ -863,7 +1043,7 @@
         <v>14</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -871,19 +1051,19 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G10" s="4">
         <v>46300.5</v>
@@ -892,7 +1072,7 @@
         <v>14</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -900,19 +1080,19 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="G11" s="4">
         <v>46300.5</v>
@@ -921,7 +1101,7 @@
         <v>14</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -929,19 +1109,19 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G12" s="4">
         <v>46300.5</v>
@@ -950,7 +1130,7 @@
         <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -958,19 +1138,19 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G13" s="4">
         <v>46300.5</v>
@@ -979,7 +1159,7 @@
         <v>14</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -987,19 +1167,19 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G14" s="4">
         <v>46300.5</v>
@@ -1008,7 +1188,7 @@
         <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -1016,28 +1196,28 @@
         <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G15" s="4">
-        <v>46300.5</v>
+        <v>46293.5</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1045,28 +1225,28 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="G16" s="4">
-        <v>46300.5</v>
+        <v>46279.5</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1074,28 +1254,28 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>59</v>
-      </c>
       <c r="G17" s="4">
-        <v>46293.5</v>
+        <v>46279.5</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1103,48 +1283,48 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="G18" s="4">
-        <v>46300.5</v>
+        <v>46279.5</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G19" s="4">
         <v>46300.5</v>
@@ -1153,27 +1333,27 @@
         <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G20" s="4">
         <v>46300.5</v>
@@ -1182,27 +1362,27 @@
         <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G21" s="4">
         <v>46300.5</v>
@@ -1211,27 +1391,27 @@
         <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>45</v>
+        <v>73</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G22" s="4">
         <v>46300.5</v>
@@ -1240,27 +1420,27 @@
         <v>14</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="G23" s="4">
         <v>46300.5</v>
@@ -1269,27 +1449,27 @@
         <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="G24" s="4">
         <v>46300.5</v>
@@ -1298,27 +1478,27 @@
         <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="G25" s="4">
         <v>46300.5</v>
@@ -1327,40 +1507,1026 @@
         <v>14</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="G26" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G30" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G31" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G32" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G33" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G35" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G36" s="4">
         <v>46293.5</v>
       </c>
-      <c r="H26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>60</v>
+      <c r="H36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G37" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G40" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G43" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G45" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G46" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G47" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G48" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G49" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G50" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G51" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G52" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G54" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46293.5</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G59" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G60" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I26"/>
+  <autoFilter ref="A1:I60"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="91">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -79,111 +79,69 @@
     <t xml:space="preserve">COLA VIPAL VIPAFIX 1KG                            </t>
   </si>
   <si>
-    <t xml:space="preserve">020605696      </t>
+    <t xml:space="preserve">010500087      </t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>000305501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAXA GADUS S3 V220 C 18KG                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010700061      </t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>000057934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROLETE INFERIOR KOMATSU 131-30                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">010500087      </t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>000305501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRAXA GADUS S3 V220 C 18KG                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">010700061      </t>
-  </si>
-  <si>
     <t>000305500</t>
   </si>
   <si>
     <t xml:space="preserve">OLEO SPIRAX S4 TXM FR 20LT                        </t>
   </si>
   <si>
+    <t xml:space="preserve">020100092      </t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>001177777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAFITE SPRAY 200ML                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020609434      </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORCA PARLOC M6                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072600157      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROLO PINTURA ANTIGOTA 09 CM                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090600296      </t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMA ROTATIVA CILINDRICA 10MM                     </t>
+  </si>
+  <si>
     <t>020202</t>
   </si>
   <si>
-    <t xml:space="preserve">020608211      </t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>000009327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA STEINERT STP20 00011/                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040400128      </t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>000008792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DESINFETANTE 5LT                                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040400159      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">VASSOURA  V-9 CONDOR UN                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040400055      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODO C CABO MADEIRA 60CM                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040400364      </t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLORO DUPLO GEL 1LT                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040400365      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMPA PISOS 5LT REMOVEX PERFECTO                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040801159      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SACO P/ LIXO 60LTS PRETO                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020800389      </t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>000010333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO SANDVIK SAHF 9524                          </t>
-  </si>
-  <si>
     <t xml:space="preserve">180200042      </t>
   </si>
   <si>
@@ -196,9 +154,6 @@
     <t xml:space="preserve">020800424      </t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t xml:space="preserve">FILTRO ATLASCOPCO 1613950300 ORIGINAL             </t>
   </si>
   <si>
@@ -295,21 +250,6 @@
     <t xml:space="preserve">CILINDRO MERCEDES A0032607463                     </t>
   </si>
   <si>
-    <t xml:space="preserve">040201933      </t>
-  </si>
-  <si>
-    <t>000062442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA MERCEDES A0001405339                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201934      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">UNIDADE MERCEDES A0001407878                      </t>
-  </si>
-  <si>
     <t xml:space="preserve">040201566      </t>
   </si>
   <si>
@@ -319,61 +259,31 @@
     <t xml:space="preserve">COXIM MERCEDES A9582411213                        </t>
   </si>
   <si>
-    <t xml:space="preserve">040201509      </t>
-  </si>
-  <si>
-    <t>000062449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLIA MERCEDES A0005501933                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040202233      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERRUPTOR COMANDO MERCEDES A0055453413          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">030200001      </t>
-  </si>
-  <si>
-    <t>000125658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTETOR ARO R24 FURO CENTRAL                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">030100012      </t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>002755950</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNEU 325/95R24                                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300110      </t>
-  </si>
-  <si>
-    <t>000849089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO CAT 273-5711                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300117      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO CAT 500-0483                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300118      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO CAT 523-4987                               </t>
+    <t xml:space="preserve">040200565      </t>
+  </si>
+  <si>
+    <t>000021102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMORTECEDOR TRASEIRO AXOR 4144 A0063266800        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201672      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LENTE DO FAROL NINO L-86 LD                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400029      </t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>000849315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO CAT 7X-7858                                  </t>
   </si>
 </sst>
 </file>
@@ -771,7 +681,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11.69" customWidth="1"/>
@@ -970,27 +880,27 @@
         <v>11</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G7" s="4">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>34</v>
@@ -1005,97 +915,97 @@
         <v>35</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="G8" s="4">
-        <v>46276.5</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G10" s="4">
-        <v>46300.5</v>
+        <v>46303.5</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="G11" s="4">
-        <v>46300.5</v>
+        <v>46279.5</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>14</v>
@@ -1106,7 +1016,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>46</v>
@@ -1115,56 +1025,56 @@
         <v>11</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46279.5</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G12" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46279.5</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="G13" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>51</v>
@@ -1173,13 +1083,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="G14" s="4">
         <v>46300.5</v>
@@ -1188,143 +1098,143 @@
         <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46293.5</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="4">
-        <v>46279.5</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G17" s="4">
-        <v>46279.5</v>
+        <v>46300.5</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G18" s="4">
-        <v>46279.5</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G19" s="4">
         <v>46300.5</v>
@@ -1333,27 +1243,27 @@
         <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G20" s="4">
         <v>46300.5</v>
@@ -1362,27 +1272,27 @@
         <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G21" s="4">
         <v>46300.5</v>
@@ -1391,146 +1301,146 @@
         <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G22" s="4">
-        <v>46300.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G23" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="G26" s="4">
-        <v>46300.5</v>
+        <v>46303.5</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>14</v>
@@ -1541,7 +1451,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>85</v>
@@ -1550,45 +1460,45 @@
         <v>11</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F27" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G27" s="4">
+        <v>46303.5</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="G27" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>61</v>
-      </c>
       <c r="E28" s="3" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G28" s="4">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>14</v>
@@ -1599,934 +1509,441 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="G29" s="4">
-        <v>46302.5</v>
+        <v>46300.5</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="G30" s="4">
-        <v>46302.5</v>
+        <v>46300.5</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>96</v>
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>95</v>
+        <v>52</v>
       </c>
       <c r="G31" s="4">
-        <v>46302.5</v>
+        <v>46300.5</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>100</v>
+        <v>52</v>
       </c>
       <c r="G32" s="4">
-        <v>46302.5</v>
+        <v>46300.5</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>102</v>
+        <v>60</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="G33" s="4">
-        <v>46302.5</v>
+        <v>46300.5</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>104</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46300.5</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G34" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>107</v>
+        <v>66</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="G35" s="4">
-        <v>46302.5</v>
+        <v>46300.5</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>109</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>111</v>
+        <v>40</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="G36" s="4">
-        <v>46293.5</v>
+        <v>46300.5</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>113</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="G37" s="4">
-        <v>46303.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>116</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>117</v>
+        <v>73</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="G38" s="4">
-        <v>46303.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>118</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="G39" s="4">
-        <v>46303.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G40" s="4">
-        <v>46300.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G41" s="4">
-        <v>46300.5</v>
+        <v>46303.5</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="G42" s="4">
-        <v>46300.5</v>
+        <v>46303.5</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="G43" s="4">
-        <v>46300.5</v>
+        <v>46303.5</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G44" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G45" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G46" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G47" s="4">
-        <v>46300.5</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G48" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G49" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I49" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G50" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G51" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G52" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G53" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G54" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G55" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G56" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="G57" s="4">
-        <v>46293.5</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G58" s="4">
-        <v>46303.5</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G59" s="4">
-        <v>46303.5</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="G60" s="4">
-        <v>46303.5</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:I60"/>
+  <autoFilter ref="A1:I43"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="264">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -73,6 +73,411 @@
     <t xml:space="preserve">ROLETE CARGA 440 (T) X 470 (E) X 127 X 20 X 14MM  </t>
   </si>
   <si>
+    <t xml:space="preserve">020100026      </t>
+  </si>
+  <si>
+    <t>000013017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAME SOLDA MIG 1,2MM 15KG VONDER                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020609440      </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORCA PARLOC M22                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800374      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABRACADEIRA ROSCA S/FIM 14X22                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800182      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABRACADEIRA DE NYLON 8,8 X 760                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072700223      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIFAO SANFONADO PVC                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072700808      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TORNEIRA ALTA DOCOL GALI                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090600006      </t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISCO SERRA CIRCULAR 110MM 24D                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090600166      </t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISCO FLAP 4.1/2 GRAO 40                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090600046      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISCO DIAMANTADO CORTAG 60598                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600327      </t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>000013015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRINCHA CONDOR 700 X 2                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800152      </t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITA ISOL 20M 33+ SCOTCH 3M                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072700628      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLA TIGRE PVC 175GR                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072700089      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGATE FLEXIVEL 1/2 60CM                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090600282      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISCO TUNGSTENIO T18 4"                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400191      </t>
+  </si>
+  <si>
+    <t>000013020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DISCO DE DESBASTE 7" DEWALT                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600110      </t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>000013021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORCA PARA GRAMPO DE CORRENTE 20MM                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600111      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORCA SEXT PARLOC PARA GRAMPO DE CORRENTE 20MM    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800359      </t>
+  </si>
+  <si>
+    <t>000013014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADESIVO ANAEROBICO LOCTITE 10G                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090500921      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA SECA P/ MACARICO VSCM-OX                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010300005      </t>
+  </si>
+  <si>
+    <t>000004397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAS R-134 13,6KG EOS                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600037      </t>
+  </si>
+  <si>
+    <t>000002155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATERIA 100AH                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020602260      </t>
+  </si>
+  <si>
+    <t>000125789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANILHA RETA PESADA 22MM                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020603999      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAMPO P/ CORREIA 2" FERA                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040801355      </t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>000067888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA TERMICA CORAL DANNY CA 15366 TAM 8           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100131      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°40                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130800049      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA TERMICA CORAL DANNY CA 15366 TAM 9           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">070603409      </t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>000033209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA S70 1/4 3/2V                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020605014      </t>
+  </si>
+  <si>
+    <t>000849626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANGUEIRA CAT 1873961.000                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020100070      </t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>000013068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILICONE TRANSP 50G                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020601725      </t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELETRODO 7018 3.25MM                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020606581      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PF FRANCES 5/8 X 5                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800592      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMA ROTATIVA CONICA 16X22X6X7                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040801118      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABRACADEIRA PLASTICA 100X2.5MM                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400474      </t>
+  </si>
+  <si>
+    <t>000009978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELEMENTO ACRIFLEX ROTEX 42                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">030500017      </t>
+  </si>
+  <si>
+    <t>000002266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNEU 265/65R17                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020800181      </t>
+  </si>
+  <si>
+    <t>000850122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 290-2287 AR CONDICIONADO               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400796      </t>
+  </si>
+  <si>
+    <t>000850137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALHETA  PORTA/LATERAL - 6V-5849                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400795      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PALHETA DIANTEIRA - 6V-5851                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020604183      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORCA CAT 2J-3507                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020605702      </t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>000134536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARRUELA KOMATSU 01643-32060XXN                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010200074      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO FLEETGUARD HF35381                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600129      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO KOMATSU 12Y-979-1174                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600130      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO KOMATSU 12Y-979-6180                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020605698      </t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAFUSO KOMATSU 01010-81670XX                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600139      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO KOMATSU 600-411-4100E                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010200080      </t>
+  </si>
+  <si>
+    <t>000001006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO FLEETGUARD AF4207                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020800327      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO FLEETGUARD AF4201                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020604221      </t>
+  </si>
+  <si>
+    <t>000000424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SENSOR XCKS141 TELEMECANIQUE                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">030400581      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHAVE SELETORA LAY5-ED3                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020901408      </t>
+  </si>
+  <si>
+    <t>000000425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELE AUXILIAR 301-10-C-R1 U02 24VDC 20A/15A       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090500384      </t>
+  </si>
+  <si>
+    <t>000000957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BICO ABAST AUT 1" ALTA VAZAO                      </t>
+  </si>
+  <si>
     <t>020202</t>
   </si>
   <si>
@@ -100,51 +505,39 @@
     <t xml:space="preserve">ROLAMENTO 6207-2RSC3                              </t>
   </si>
   <si>
+    <t xml:space="preserve">130700022      </t>
+  </si>
+  <si>
+    <t>000002279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPUZ BALACLAVA ARABE CA - 40147                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100160      </t>
+  </si>
+  <si>
+    <t>000068063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-34554 N°41                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100133      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°42                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100134      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°43                     </t>
+  </si>
+  <si>
     <t>020302</t>
   </si>
   <si>
-    <t xml:space="preserve">072700074      </t>
-  </si>
-  <si>
-    <t>001173173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHUMBADOR PARABOLT PBC 5/8 X 5                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020100111      </t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIXA FERRO GR 100                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040800188      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">RODA LIXA 60 X 20MM GR                            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020100262      </t>
-  </si>
-  <si>
-    <t>001173004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRA ROSCADA 5/8 UNC PL                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">090600059      </t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DISCO CORTE 7X1.6X7/8 DW8065                      </t>
-  </si>
-  <si>
     <t xml:space="preserve">020901419      </t>
   </si>
   <si>
@@ -160,15 +553,66 @@
     <t xml:space="preserve">CONTATOR XTCE 025 C10 ETN 24VDC DIL M25-10        </t>
   </si>
   <si>
+    <t xml:space="preserve">020900502      </t>
+  </si>
+  <si>
+    <t>004514924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMI REMOTA CFW500-HMIR                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020900858      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CJ CABO IHM WEG CFW500-CCHMIR05M                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">070601138      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVERSOR WEG 15180353 CFW500G0180T4DB20C3H00G2    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">070602030      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MODULO COMUNICACAO CFW500-CRS4B                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130500001      </t>
+  </si>
+  <si>
+    <t>000067895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABAFADOR SEM HASTE CA-27971                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100130      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°39                     </t>
+  </si>
+  <si>
+    <t>000163866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130800006      </t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA POLIESTER TAM G (9) CA-37266 / CA 50754      </t>
+  </si>
+  <si>
     <t>100106</t>
   </si>
   <si>
     <t xml:space="preserve">040300114      </t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>000849060</t>
   </si>
   <si>
@@ -199,9 +643,6 @@
     <t xml:space="preserve">040201703      </t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t xml:space="preserve">ABRACADEIRA 80/60 N10223                          </t>
   </si>
   <si>
@@ -226,9 +667,6 @@
     <t xml:space="preserve">040201693      </t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t xml:space="preserve">RETENTOR MERCEDES A0139977346                     </t>
   </si>
   <si>
@@ -248,6 +686,123 @@
   </si>
   <si>
     <t xml:space="preserve">ANEL MERCEDES N912009035100                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201692      </t>
+  </si>
+  <si>
+    <t>000048734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA KNORR LI 31319                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300009      </t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO MANN CF-1651                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200612      </t>
+  </si>
+  <si>
+    <t>000048733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPRESSOR WABCO 8869025190193                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201192      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUNTA MERCEDES A4571310180                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040202167      </t>
+  </si>
+  <si>
+    <t>000048718</t>
+  </si>
+  <si>
+    <t>CILINDRO DE COMANDO DO GP CAMBIO RANGE A0022609563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300131      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO TANQUE HIDR BASC HYVA 14896992A            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800201      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUICA DE FREIO MERCEDES DIANTEIRO LE A9584200324  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200746      </t>
+  </si>
+  <si>
+    <t>000048717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA MERCEDES A0024319215 6VIAS AXOR 4144      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200063      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUICA DE FREIO MERCEDES DIANTEIRO LD A 9584200224 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400008      </t>
+  </si>
+  <si>
+    <t>000282883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO PETRONAS ATO 220 ISO VG 220                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400036      </t>
+  </si>
+  <si>
+    <t>000398227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO MOBIL 80W 20LT                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400037      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO 10W40 MOBIL 20LT                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300116      </t>
+  </si>
+  <si>
+    <t>000849917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 496-9841                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300154      </t>
+  </si>
+  <si>
+    <t>000000331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT 500HS CHICAGO PNEUMATIC CPS350-10             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300155      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT 1000HS CHICAGO PNEUMATIC CPS350-10            </t>
   </si>
 </sst>
 </file>
@@ -645,7 +1200,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I126"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15.06" customWidth="1"/>
@@ -748,54 +1303,54 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="G4" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>14</v>
@@ -806,7 +1361,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>26</v>
@@ -815,30 +1370,30 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>11</v>
@@ -850,140 +1405,140 @@
         <v>17</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G7" s="4">
-        <v>46291.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" s="4">
-        <v>46291.5</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="G9" s="4">
-        <v>46291.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="G10" s="4">
-        <v>46291.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46291.5</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>11</v>
@@ -995,687 +1550,3326 @@
         <v>12</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="G12" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="G13" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="G14" s="4">
-        <v>46302.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C15" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G15" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G16" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="G17" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G18" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G19" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>17</v>
+        <v>59</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G20" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G21" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G22" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G23" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="G24" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="G25" s="4">
-        <v>46302.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G26" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G27" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>62</v>
+        <v>81</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="G28" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>51</v>
+        <v>12</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="G29" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="G30" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="G31" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>71</v>
+        <v>24</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="G32" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="G33" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="G34" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>76</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="G35" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G36" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G37" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G40" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G43" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G45" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G46" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G47" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G48" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G49" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G50" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G51" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G52" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G53" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G54" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G56" s="4">
         <v>46308.5</v>
       </c>
-      <c r="H35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>78</v>
+      <c r="H56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G59" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G60" s="4">
+        <v>46310.5</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G61" s="4">
+        <v>46310.5</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G62" s="4">
+        <v>46310.5</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G63" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G64" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G66" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G67" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="G68" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G69" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G70" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G71" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G72" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G73" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G74" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G75" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G76" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G77" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G78" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G79" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G80" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G81" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G82" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G83" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G84" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G85" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G86" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G87" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G88" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G89" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G90" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G91" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G92" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G93" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G94" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G95" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G96" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G97" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G98" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G99" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G100" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G101" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G102" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G103" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G104" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G105" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G106" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G107" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G108" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G109" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G110" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G111" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G112" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="G113" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G114" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="G115" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G116" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G117" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="G118" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G119" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G120" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G121" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G122" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G123" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G124" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G125" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G126" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>263</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I35"/>
+  <autoFilter ref="A1:I126"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="351">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -535,21 +535,156 @@
     <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°43                     </t>
   </si>
   <si>
+    <t xml:space="preserve">040800684      </t>
+  </si>
+  <si>
+    <t>000008812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMPADOR GEL ESTRELA MARINE 5LT                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400137      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALCOOL GEL 70° 500ML                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400221      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMPA ALUM PASTA 500GR ALUMIL                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400160      </t>
+  </si>
+  <si>
+    <t>000008813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESPONJA ACO 60GR BOMBRIL UN                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400010      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SABONETE LIQUIDO 5LTS                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400051      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODO C CABO 40CM                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400099      </t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANO MICROFIBRA 60X80                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800440      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPO DESC TRANSP 100X200ML                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800866      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RODO ALUMINIO 50CM                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800623      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SACO DE LIXO 100LT CINZA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020100038      </t>
+  </si>
+  <si>
+    <t>000008801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PANO WIPER 750/600 FOLHAS                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400005      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUA SANITARIA 2LT                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800360      </t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PILHA ALCALINA AA 2X1                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800510      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPO DESC 100X50ML                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400553      </t>
+  </si>
+  <si>
+    <t>000028434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENEIRA 1410X2900 50,8-2" GANCHO C/CAPA VL2900MM  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040801178      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PENEIRA 2100X2730 25,4-1" GANCHO C/CAPA VL2750MM  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020604635      </t>
+  </si>
+  <si>
+    <t>000028435</t>
+  </si>
+  <si>
+    <t>PENEIRA 1410X2170 12,7-1/2" GANCHO C/CAPA VL2170MM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400408      </t>
+  </si>
+  <si>
+    <t>000028433</t>
+  </si>
+  <si>
+    <t>PENEIRA 1410X2900 12,7-1/2" GANCHO C/CAPA VL2900MM</t>
+  </si>
+  <si>
     <t>020302</t>
   </si>
   <si>
-    <t xml:space="preserve">020901419      </t>
+    <t xml:space="preserve">130600078      </t>
+  </si>
+  <si>
+    <t>000002215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCA NR10 CLASSE2 CA-41.147 G AZUL ESCURO        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020901420      </t>
   </si>
   <si>
     <t>001629223</t>
   </si>
   <si>
-    <t xml:space="preserve">CONTATOR XTCE 025 C01 ETN 220V                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020901420      </t>
-  </si>
-  <si>
     <t xml:space="preserve">CONTATOR XTCE 025 C10 ETN 24VDC DIL M25-10        </t>
   </si>
   <si>
@@ -607,6 +742,30 @@
     <t xml:space="preserve">LUVA POLIESTER TAM G (9) CA-37266 / CA 50754      </t>
   </si>
   <si>
+    <t xml:space="preserve">130100132      </t>
+  </si>
+  <si>
+    <t>001033929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°41                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130800030      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA LATEX CA-15100 TAM 8                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130300035      </t>
+  </si>
+  <si>
+    <t>1.020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESPIRADOR PFF2 BRANCO CA-5657                    </t>
+  </si>
+  <si>
     <t>100106</t>
   </si>
   <si>
@@ -700,9 +859,6 @@
     <t xml:space="preserve">040300009      </t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t xml:space="preserve">FILTRO MANN CF-1651                               </t>
   </si>
   <si>
@@ -803,6 +959,111 @@
   </si>
   <si>
     <t xml:space="preserve">KIT 1000HS CHICAGO PNEUMATIC CPS350-10            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201545      </t>
+  </si>
+  <si>
+    <t>000097291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MOLA TRAS AXOX4144 MRB16206                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201546      </t>
+  </si>
+  <si>
+    <t>000097293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 MOLA TRAS AXOX4144 MRB16207                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201847      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MOLA DIANT AXOR4144 MRB18304                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200813      </t>
+  </si>
+  <si>
+    <t>000062617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JG TAMPA MERCEDES A 9433300956                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201494      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABRACADEIRA MERCEDES N1467                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040202237      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAFUSO MERCEDES N000000005729 M20X1,5X100       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090100042      </t>
+  </si>
+  <si>
+    <t>000002440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°36                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090100046      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090100048      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090500016      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTETOR SOLAR 60FPS 120G                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090600013      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPUZ BALACLAVA CA-10979                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201694      </t>
+  </si>
+  <si>
+    <t>000062495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERRUPTOR MERCEDES A9585452107                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201861      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBULACAO MERCEDES A6954760801                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300126      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO MERCEDES A 0001421089                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400059      </t>
+  </si>
+  <si>
+    <t>INTERRUPTOR DA TOMADA DE FORCA MERCEDES A958545030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201492      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABRAC. MERCEDES N000000002775                     </t>
   </si>
 </sst>
 </file>
@@ -1200,7 +1461,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I126"/>
+  <dimension ref="A1:I182"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15.06" customWidth="1"/>
@@ -3014,474 +3275,474 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="2" t="s">
+      <c r="G63" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="G63" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G64" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G64" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B65" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G65" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B66" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G66" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I66" s="2" t="s">
         <v>183</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G66" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B67" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G67" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I67" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G67" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G68" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I68" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="G68" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C69" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="E69" s="3" t="s">
-        <v>35</v>
+        <v>189</v>
       </c>
       <c r="F69" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G69" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I69" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="G69" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G70" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="G70" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="F71" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="G71" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I71" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="G71" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="G72" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G73" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>196</v>
+        <v>96</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G74" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>200</v>
-      </c>
       <c r="G75" s="4">
-        <v>46302.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B76" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>204</v>
-      </c>
       <c r="G76" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G77" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>35</v>
+        <v>89</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G78" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>11</v>
@@ -3493,82 +3754,82 @@
         <v>24</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="G79" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>24</v>
+        <v>125</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="G80" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>198</v>
+        <v>155</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="G81" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>11</v>
@@ -3580,24 +3841,24 @@
         <v>81</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="G82" s="4">
-        <v>46308.5</v>
+        <v>46296.5</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>11</v>
@@ -3609,7 +3870,7 @@
         <v>12</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="G83" s="4">
         <v>46308.5</v>
@@ -3618,82 +3879,82 @@
         <v>14</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="G84" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>207</v>
+        <v>226</v>
       </c>
       <c r="G85" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>226</v>
@@ -3705,24 +3966,24 @@
         <v>14</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>229</v>
+        <v>12</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>229</v>
+        <v>12</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>226</v>
@@ -3734,27 +3995,27 @@
         <v>14</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G88" s="4">
         <v>46309.5</v>
@@ -3763,27 +4024,27 @@
         <v>14</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="G89" s="4">
         <v>46309.5</v>
@@ -3792,27 +4053,27 @@
         <v>14</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>236</v>
+        <v>84</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G90" s="4">
         <v>46309.5</v>
@@ -3821,28 +4082,28 @@
         <v>14</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>238</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B91" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F91" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="G91" s="4">
         <v>46309.5</v>
       </c>
@@ -3850,27 +4111,27 @@
         <v>14</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>240</v>
+        <v>171</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G92" s="4">
         <v>46309.5</v>
@@ -3879,27 +4140,27 @@
         <v>14</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>242</v>
+        <v>173</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>12</v>
+        <v>241</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="G93" s="4">
         <v>46309.5</v>
@@ -3908,146 +4169,146 @@
         <v>14</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>244</v>
       </c>
       <c r="G94" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="G95" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>35</v>
+        <v>249</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G96" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B97" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G97" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="G97" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="E98" s="3" t="s">
-        <v>12</v>
+        <v>256</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>257</v>
       </c>
       <c r="G98" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>14</v>
@@ -4058,7 +4319,7 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>259</v>
@@ -4076,7 +4337,7 @@
         <v>260</v>
       </c>
       <c r="G99" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>14</v>
@@ -4087,7 +4348,7 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>262</v>
@@ -4096,16 +4357,16 @@
         <v>11</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>260</v>
       </c>
       <c r="G100" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>14</v>
@@ -4116,10 +4377,10 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>199</v>
+        <v>264</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>11</v>
@@ -4131,36 +4392,36 @@
         <v>24</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="G101" s="4">
-        <v>46302.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>203</v>
+        <v>24</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>203</v>
+        <v>24</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>204</v>
+        <v>260</v>
       </c>
       <c r="G102" s="4">
         <v>46308.5</v>
@@ -4169,27 +4430,27 @@
         <v>14</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>205</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="G103" s="4">
         <v>46308.5</v>
@@ -4198,27 +4459,27 @@
         <v>14</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>208</v>
+        <v>269</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="G104" s="4">
         <v>46308.5</v>
@@ -4227,27 +4488,27 @@
         <v>14</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>210</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>211</v>
+        <v>272</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="G105" s="4">
         <v>46308.5</v>
@@ -4256,15 +4517,15 @@
         <v>14</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>212</v>
+        <v>273</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>213</v>
+        <v>274</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>11</v>
@@ -4276,7 +4537,7 @@
         <v>24</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="G106" s="4">
         <v>46308.5</v>
@@ -4285,27 +4546,27 @@
         <v>14</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>215</v>
+        <v>276</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>207</v>
+        <v>260</v>
       </c>
       <c r="G107" s="4">
         <v>46308.5</v>
@@ -4314,73 +4575,73 @@
         <v>14</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>216</v>
+        <v>277</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>217</v>
+        <v>278</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>207</v>
+        <v>279</v>
       </c>
       <c r="G108" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>218</v>
+        <v>280</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>12</v>
+        <v>189</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>12</v>
+        <v>189</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>207</v>
+        <v>279</v>
       </c>
       <c r="G109" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>220</v>
+        <v>282</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>221</v>
+        <v>283</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>11</v>
@@ -4392,53 +4653,53 @@
         <v>24</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>207</v>
+        <v>284</v>
       </c>
       <c r="G110" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>222</v>
+        <v>285</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>223</v>
+        <v>286</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>207</v>
+        <v>284</v>
       </c>
       <c r="G111" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>224</v>
+        <v>287</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>225</v>
+        <v>288</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>11</v>
@@ -4450,7 +4711,7 @@
         <v>12</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>226</v>
+        <v>289</v>
       </c>
       <c r="G112" s="4">
         <v>46309.5</v>
@@ -4459,27 +4720,27 @@
         <v>14</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>227</v>
+        <v>290</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>228</v>
+        <v>291</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>229</v>
+        <v>24</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>229</v>
+        <v>24</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>226</v>
+        <v>289</v>
       </c>
       <c r="G113" s="4">
         <v>46309.5</v>
@@ -4488,27 +4749,27 @@
         <v>14</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>230</v>
+        <v>292</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>231</v>
+        <v>293</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>232</v>
+        <v>289</v>
       </c>
       <c r="G114" s="4">
         <v>46309.5</v>
@@ -4517,27 +4778,27 @@
         <v>14</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>233</v>
+        <v>294</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>234</v>
+        <v>295</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>232</v>
+        <v>296</v>
       </c>
       <c r="G115" s="4">
         <v>46309.5</v>
@@ -4546,27 +4807,27 @@
         <v>14</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>235</v>
+        <v>297</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>236</v>
+        <v>298</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>237</v>
+        <v>296</v>
       </c>
       <c r="G116" s="4">
         <v>46309.5</v>
@@ -4575,27 +4836,27 @@
         <v>14</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>238</v>
+        <v>299</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>239</v>
+        <v>300</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>237</v>
+        <v>301</v>
       </c>
       <c r="G117" s="4">
         <v>46309.5</v>
@@ -4604,27 +4865,27 @@
         <v>14</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>240</v>
+        <v>302</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>241</v>
+        <v>303</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="G118" s="4">
         <v>46309.5</v>
@@ -4633,27 +4894,27 @@
         <v>14</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>242</v>
+        <v>305</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>243</v>
+        <v>306</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>244</v>
+        <v>304</v>
       </c>
       <c r="G119" s="4">
         <v>46309.5</v>
@@ -4662,27 +4923,27 @@
         <v>14</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>245</v>
+        <v>307</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>244</v>
+        <v>309</v>
       </c>
       <c r="G120" s="4">
         <v>46309.5</v>
@@ -4691,27 +4952,27 @@
         <v>14</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>247</v>
+        <v>310</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>248</v>
+        <v>311</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>249</v>
+        <v>312</v>
       </c>
       <c r="G121" s="4">
         <v>46309.5</v>
@@ -4720,27 +4981,27 @@
         <v>14</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>250</v>
+        <v>313</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>251</v>
+        <v>314</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>252</v>
+        <v>312</v>
       </c>
       <c r="G122" s="4">
         <v>46309.5</v>
@@ -4749,15 +5010,15 @@
         <v>14</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>253</v>
+        <v>315</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>254</v>
+        <v>316</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>11</v>
@@ -4769,107 +5030,1731 @@
         <v>24</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>252</v>
+        <v>317</v>
       </c>
       <c r="G123" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>255</v>
+        <v>318</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>256</v>
+        <v>319</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>257</v>
+        <v>320</v>
       </c>
       <c r="G124" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>258</v>
+        <v>321</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>259</v>
+        <v>322</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>260</v>
+        <v>320</v>
       </c>
       <c r="G125" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>261</v>
+        <v>323</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>198</v>
+        <v>251</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G126" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G127" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G128" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E129" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G129" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G130" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G131" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G132" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G133" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G134" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G135" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G136" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E137" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G137" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E138" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G138" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E139" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G139" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E140" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="G140" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E141" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="G141" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G142" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="C126" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F126" s="2" t="s">
+      <c r="C143" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F143" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="G126" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I126" s="2" t="s">
+      <c r="G143" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I143" s="2" t="s">
         <v>263</v>
       </c>
     </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G144" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G145" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E146" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G146" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G147" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G148" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E149" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G149" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="G150" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G151" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="G152" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G153" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G154" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G155" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G156" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="G157" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G158" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G159" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="G160" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G161" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G162" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G163" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G164" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="G165" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E166" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="G166" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G167" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="G168" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E169" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G169" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G170" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G171" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="G172" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G173" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E174" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G174" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G175" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E176" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G176" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E177" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="G177" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E178" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G178" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E179" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G179" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E180" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G180" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E181" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G181" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E182" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="G182" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I126"/>
+  <autoFilter ref="A1:I182"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1457" uniqueCount="351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="361">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -476,6 +476,36 @@
   </si>
   <si>
     <t xml:space="preserve">BICO ABAST AUT 1" ALTA VAZAO                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020900025      </t>
+  </si>
+  <si>
+    <t>000003260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMPADA H4 12V                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">030400582      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELE AUXILIAR 12V 40AMP 5 PINO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020900818      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">GIROFLEX DNI 24LED BIVOLT                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020601473      </t>
+  </si>
+  <si>
+    <t>000021179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEL P/ MONTAGEM OR 25 17.5 - 25                  </t>
   </si>
   <si>
     <t>020202</t>
@@ -1461,7 +1491,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I182"/>
+  <dimension ref="A1:I186"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15.06" customWidth="1"/>
@@ -3072,199 +3102,199 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B56" s="2" t="s">
+      <c r="C56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C56" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="G56" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="G56" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>155</v>
+        <v>9</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I57" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G57" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>155</v>
+        <v>9</v>
       </c>
       <c r="B58" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="G58" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>155</v>
+        <v>9</v>
       </c>
       <c r="B59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G59" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I59" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G59" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="2" t="s">
+      <c r="G60" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="G60" s="4">
-        <v>46310.5</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G61" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G61" s="4">
-        <v>46310.5</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="C62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="G62" s="4">
-        <v>46310.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>14</v>
@@ -3275,7 +3305,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>174</v>
@@ -3284,16 +3314,16 @@
         <v>11</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>175</v>
       </c>
       <c r="G63" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>14</v>
@@ -3304,7 +3334,7 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>177</v>
@@ -3313,74 +3343,74 @@
         <v>11</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G64" s="4">
-        <v>46311.5</v>
+        <v>46310.5</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G65" s="4">
-        <v>46311.5</v>
+        <v>46310.5</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G66" s="4">
-        <v>46311.5</v>
+        <v>46310.5</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>14</v>
@@ -3391,7 +3421,7 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>184</v>
@@ -3400,13 +3430,13 @@
         <v>11</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G67" s="4">
         <v>46311.5</v>
@@ -3415,27 +3445,27 @@
         <v>14</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G68" s="4">
         <v>46311.5</v>
@@ -3444,27 +3474,27 @@
         <v>14</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>189</v>
+        <v>17</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="G69" s="4">
         <v>46311.5</v>
@@ -3478,7 +3508,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>191</v>
@@ -3493,7 +3523,7 @@
         <v>17</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G70" s="4">
         <v>46311.5</v>
@@ -3502,15 +3532,15 @@
         <v>14</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>11</v>
@@ -3522,7 +3552,7 @@
         <v>35</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G71" s="4">
         <v>46311.5</v>
@@ -3531,27 +3561,27 @@
         <v>14</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>96</v>
+        <v>12</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="G72" s="4">
         <v>46311.5</v>
@@ -3560,27 +3590,27 @@
         <v>14</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G73" s="4">
         <v>46311.5</v>
@@ -3589,27 +3619,27 @@
         <v>14</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G74" s="4">
         <v>46311.5</v>
@@ -3618,27 +3648,27 @@
         <v>14</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>203</v>
+        <v>35</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G75" s="4">
         <v>46311.5</v>
@@ -3652,7 +3682,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>205</v>
@@ -3661,13 +3691,13 @@
         <v>11</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G76" s="4">
         <v>46311.5</v>
@@ -3681,7 +3711,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>207</v>
@@ -3690,10 +3720,10 @@
         <v>11</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>208</v>
@@ -3710,7 +3740,7 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>210</v>
@@ -3719,10 +3749,10 @@
         <v>11</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>208</v>
@@ -3739,7 +3769,7 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>212</v>
@@ -3748,13 +3778,13 @@
         <v>11</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>24</v>
+        <v>213</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>24</v>
+        <v>213</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="G79" s="4">
         <v>46311.5</v>
@@ -3768,7 +3798,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>215</v>
@@ -3777,13 +3807,13 @@
         <v>11</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="G80" s="4">
         <v>46311.5</v>
@@ -3792,15 +3822,15 @@
         <v>14</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>11</v>
@@ -3812,7 +3842,7 @@
         <v>12</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G81" s="4">
         <v>46311.5</v>
@@ -3821,30 +3851,30 @@
         <v>14</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="G82" s="4">
-        <v>46296.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>14</v>
@@ -3855,7 +3885,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>218</v>
+        <v>165</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>222</v>
@@ -3864,16 +3894,16 @@
         <v>11</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>223</v>
       </c>
       <c r="G83" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>14</v>
@@ -3884,7 +3914,7 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>218</v>
+        <v>165</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>225</v>
@@ -3893,16 +3923,16 @@
         <v>11</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>226</v>
       </c>
       <c r="G84" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>14</v>
@@ -3913,54 +3943,54 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>218</v>
+        <v>165</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>226</v>
       </c>
       <c r="G85" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B86" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F86" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="G86" s="4">
-        <v>46309.5</v>
+        <v>46296.5</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>14</v>
@@ -3971,7 +4001,7 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>232</v>
@@ -3986,36 +4016,36 @@
         <v>12</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="G87" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G88" s="4">
         <v>46309.5</v>
@@ -4024,27 +4054,27 @@
         <v>14</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>81</v>
+        <v>35</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="G89" s="4">
         <v>46309.5</v>
@@ -4053,27 +4083,27 @@
         <v>14</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G90" s="4">
         <v>46309.5</v>
@@ -4082,27 +4112,27 @@
         <v>14</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>85</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>170</v>
+        <v>242</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G91" s="4">
         <v>46309.5</v>
@@ -4111,27 +4141,27 @@
         <v>14</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>171</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>172</v>
+        <v>244</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G92" s="4">
         <v>46309.5</v>
@@ -4140,27 +4170,27 @@
         <v>14</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>173</v>
+        <v>246</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>241</v>
+        <v>81</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="G93" s="4">
         <v>46309.5</v>
@@ -4169,259 +4199,259 @@
         <v>14</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>243</v>
+        <v>84</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G94" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>245</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G95" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>247</v>
+        <v>181</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>248</v>
+        <v>182</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>244</v>
-      </c>
       <c r="G96" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>250</v>
+        <v>183</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="B97" s="2" t="s">
+      <c r="E97" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G97" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I97" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G97" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G98" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="G98" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G99" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>251</v>
+        <v>228</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>35</v>
+        <v>259</v>
       </c>
       <c r="F100" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G100" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I100" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="G100" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H100" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B101" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G101" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I101" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F101" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G101" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B102" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="E102" s="3" t="s">
-        <v>24</v>
+        <v>266</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="G102" s="4">
         <v>46308.5</v>
@@ -4430,27 +4460,27 @@
         <v>14</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G103" s="4">
         <v>46308.5</v>
@@ -4459,27 +4489,27 @@
         <v>14</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B104" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F104" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F104" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="G104" s="4">
         <v>46308.5</v>
@@ -4488,27 +4518,27 @@
         <v>14</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G105" s="4">
         <v>46308.5</v>
@@ -4517,15 +4547,15 @@
         <v>14</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>11</v>
@@ -4537,7 +4567,7 @@
         <v>24</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G106" s="4">
         <v>46308.5</v>
@@ -4546,27 +4576,27 @@
         <v>14</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G107" s="4">
         <v>46308.5</v>
@@ -4575,73 +4605,73 @@
         <v>14</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="G108" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="G109" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>11</v>
@@ -4653,10 +4683,10 @@
         <v>24</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="G110" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>14</v>
@@ -4667,7 +4697,7 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>286</v>
@@ -4676,16 +4706,16 @@
         <v>11</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="G111" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>14</v>
@@ -4696,7 +4726,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>288</v>
@@ -4725,7 +4755,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>291</v>
@@ -4734,10 +4764,10 @@
         <v>11</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>289</v>
@@ -4754,7 +4784,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>293</v>
@@ -4763,13 +4793,13 @@
         <v>11</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G114" s="4">
         <v>46309.5</v>
@@ -4778,27 +4808,27 @@
         <v>14</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G115" s="4">
         <v>46309.5</v>
@@ -4812,7 +4842,7 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>298</v>
@@ -4821,13 +4851,13 @@
         <v>11</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G116" s="4">
         <v>46309.5</v>
@@ -4836,27 +4866,27 @@
         <v>14</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G117" s="4">
         <v>46309.5</v>
@@ -4870,7 +4900,7 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>303</v>
@@ -4879,42 +4909,42 @@
         <v>11</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="F118" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G118" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I118" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="G118" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B119" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F119" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="G119" s="4">
         <v>46309.5</v>
@@ -4928,7 +4958,7 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>308</v>
@@ -4937,71 +4967,71 @@
         <v>11</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F120" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G120" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I120" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="G120" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B121" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F121" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C121" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F121" s="2" t="s">
+      <c r="G121" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I121" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="G121" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="G122" s="4">
         <v>46309.5</v>
@@ -5015,7 +5045,7 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>316</v>
@@ -5030,68 +5060,68 @@
         <v>24</v>
       </c>
       <c r="F123" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G123" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I123" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="G123" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B124" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F124" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F124" s="2" t="s">
+      <c r="G124" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I124" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="G124" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F125" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C125" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="G125" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>14</v>
@@ -5102,7 +5132,7 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>324</v>
@@ -5111,30 +5141,30 @@
         <v>11</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="F126" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G126" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I126" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="G126" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>11</v>
@@ -5146,7 +5176,7 @@
         <v>24</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G127" s="4">
         <v>46311.5</v>
@@ -5155,27 +5185,27 @@
         <v>14</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>265</v>
+        <v>328</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G128" s="4">
         <v>46311.5</v>
@@ -5184,27 +5214,27 @@
         <v>14</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G129" s="4">
         <v>46311.5</v>
@@ -5213,27 +5243,27 @@
         <v>14</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G130" s="4">
         <v>46311.5</v>
@@ -5242,27 +5272,27 @@
         <v>14</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>334</v>
+        <v>274</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G131" s="4">
         <v>46311.5</v>
@@ -5271,27 +5301,27 @@
         <v>14</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>85</v>
+        <v>275</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B132" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F132" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="C132" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D132" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E132" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="G132" s="4">
         <v>46311.5</v>
@@ -5300,27 +5330,27 @@
         <v>14</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>171</v>
+        <v>338</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G133" s="4">
         <v>46311.5</v>
@@ -5329,27 +5359,27 @@
         <v>14</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="G134" s="4">
         <v>46311.5</v>
@@ -5358,27 +5388,27 @@
         <v>14</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G135" s="4">
         <v>46311.5</v>
@@ -5387,15 +5417,15 @@
         <v>14</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>342</v>
+        <v>85</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>11</v>
@@ -5407,7 +5437,7 @@
         <v>24</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G136" s="4">
         <v>46311.5</v>
@@ -5416,27 +5446,27 @@
         <v>14</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>344</v>
+        <v>181</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G137" s="4">
         <v>46311.5</v>
@@ -5445,27 +5475,27 @@
         <v>14</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G138" s="4">
         <v>46311.5</v>
@@ -5474,27 +5504,27 @@
         <v>14</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="G139" s="4">
         <v>46311.5</v>
@@ -5503,15 +5533,15 @@
         <v>14</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>252</v>
+        <v>353</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>11</v>
@@ -5523,152 +5553,152 @@
         <v>24</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>253</v>
+        <v>351</v>
       </c>
       <c r="G140" s="4">
-        <v>46302.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>254</v>
+        <v>354</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>255</v>
+        <v>355</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>256</v>
+        <v>24</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>256</v>
+        <v>24</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>257</v>
+        <v>351</v>
       </c>
       <c r="G141" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>258</v>
+        <v>356</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>259</v>
+        <v>357</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>260</v>
+        <v>351</v>
       </c>
       <c r="G142" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>261</v>
+        <v>358</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>262</v>
+        <v>359</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>260</v>
+        <v>351</v>
       </c>
       <c r="G143" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>263</v>
+        <v>360</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="G144" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I144" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D144" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E144" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G144" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H144" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I144" s="2" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B145" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D145" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="C145" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D145" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="E145" s="3" t="s">
-        <v>24</v>
+        <v>266</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="G145" s="4">
         <v>46308.5</v>
@@ -5677,27 +5707,27 @@
         <v>14</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G146" s="4">
         <v>46308.5</v>
@@ -5706,27 +5736,27 @@
         <v>14</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F147" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D147" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E147" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F147" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="G147" s="4">
         <v>46308.5</v>
@@ -5735,27 +5765,27 @@
         <v>14</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G148" s="4">
         <v>46308.5</v>
@@ -5764,15 +5794,15 @@
         <v>14</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>11</v>
@@ -5784,7 +5814,7 @@
         <v>24</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G149" s="4">
         <v>46308.5</v>
@@ -5793,27 +5823,27 @@
         <v>14</v>
       </c>
       <c r="I149" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G150" s="4">
         <v>46308.5</v>
@@ -5822,73 +5852,73 @@
         <v>14</v>
       </c>
       <c r="I150" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="G151" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I151" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>189</v>
+        <v>12</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="G152" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I152" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>11</v>
@@ -5900,10 +5930,10 @@
         <v>24</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="G153" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>14</v>
@@ -5914,7 +5944,7 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>286</v>
@@ -5923,16 +5953,16 @@
         <v>11</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>284</v>
+        <v>270</v>
       </c>
       <c r="G154" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>14</v>
@@ -5943,7 +5973,7 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>288</v>
@@ -5972,7 +6002,7 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>291</v>
@@ -5981,10 +6011,10 @@
         <v>11</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="F156" s="2" t="s">
         <v>289</v>
@@ -6001,7 +6031,7 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>293</v>
@@ -6010,13 +6040,13 @@
         <v>11</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="G157" s="4">
         <v>46309.5</v>
@@ -6025,27 +6055,27 @@
         <v>14</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G158" s="4">
         <v>46309.5</v>
@@ -6059,7 +6089,7 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>298</v>
@@ -6068,13 +6098,13 @@
         <v>11</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="G159" s="4">
         <v>46309.5</v>
@@ -6083,27 +6113,27 @@
         <v>14</v>
       </c>
       <c r="I159" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G160" s="4">
         <v>46309.5</v>
@@ -6117,7 +6147,7 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>303</v>
@@ -6126,42 +6156,42 @@
         <v>11</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="F161" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G161" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I161" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="G161" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H161" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I161" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D162" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E162" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F162" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="G162" s="4">
         <v>46309.5</v>
@@ -6175,7 +6205,7 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>308</v>
@@ -6184,71 +6214,71 @@
         <v>11</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="F163" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G163" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I163" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="G163" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H163" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B164" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="C164" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D164" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E164" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F164" s="2" t="s">
+      <c r="G164" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I164" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="G164" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H164" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I164" s="2" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B165" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F165" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="C165" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D165" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E165" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F165" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="G165" s="4">
         <v>46309.5</v>
@@ -6262,7 +6292,7 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>316</v>
@@ -6277,68 +6307,68 @@
         <v>24</v>
       </c>
       <c r="F166" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="G166" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I166" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="G166" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H166" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I166" s="2" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B167" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E167" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C167" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D167" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E167" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F167" s="2" t="s">
+      <c r="G167" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I167" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="G167" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H167" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I167" s="2" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B168" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E168" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F168" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C168" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D168" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E168" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F168" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="G168" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>14</v>
@@ -6349,7 +6379,7 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B169" s="2" t="s">
         <v>324</v>
@@ -6358,30 +6388,30 @@
         <v>11</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>89</v>
+        <v>24</v>
       </c>
       <c r="F169" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G169" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I169" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="G169" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H169" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I169" s="2" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>264</v>
+        <v>326</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>11</v>
@@ -6393,7 +6423,7 @@
         <v>24</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G170" s="4">
         <v>46311.5</v>
@@ -6402,27 +6432,27 @@
         <v>14</v>
       </c>
       <c r="I170" s="2" t="s">
-        <v>265</v>
+        <v>328</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G171" s="4">
         <v>46311.5</v>
@@ -6431,27 +6461,27 @@
         <v>14</v>
       </c>
       <c r="I171" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="G172" s="4">
         <v>46311.5</v>
@@ -6460,27 +6490,27 @@
         <v>14</v>
       </c>
       <c r="I172" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G173" s="4">
         <v>46311.5</v>
@@ -6489,27 +6519,27 @@
         <v>14</v>
       </c>
       <c r="I173" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>334</v>
+        <v>274</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G174" s="4">
         <v>46311.5</v>
@@ -6518,27 +6548,27 @@
         <v>14</v>
       </c>
       <c r="I174" s="2" t="s">
-        <v>85</v>
+        <v>275</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B175" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E175" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F175" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="C175" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D175" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E175" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F175" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="G175" s="4">
         <v>46311.5</v>
@@ -6547,27 +6577,27 @@
         <v>14</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>171</v>
+        <v>338</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G176" s="4">
         <v>46311.5</v>
@@ -6576,27 +6606,27 @@
         <v>14</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="G177" s="4">
         <v>46311.5</v>
@@ -6605,27 +6635,27 @@
         <v>14</v>
       </c>
       <c r="I177" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G178" s="4">
         <v>46311.5</v>
@@ -6634,15 +6664,15 @@
         <v>14</v>
       </c>
       <c r="I178" s="2" t="s">
-        <v>342</v>
+        <v>85</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>11</v>
@@ -6654,7 +6684,7 @@
         <v>24</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G179" s="4">
         <v>46311.5</v>
@@ -6663,27 +6693,27 @@
         <v>14</v>
       </c>
       <c r="I179" s="2" t="s">
-        <v>344</v>
+        <v>181</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G180" s="4">
         <v>46311.5</v>
@@ -6692,27 +6722,27 @@
         <v>14</v>
       </c>
       <c r="I180" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G181" s="4">
         <v>46311.5</v>
@@ -6721,27 +6751,27 @@
         <v>14</v>
       </c>
       <c r="I181" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="G182" s="4">
         <v>46311.5</v>
@@ -6750,11 +6780,127 @@
         <v>14</v>
       </c>
       <c r="I182" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E183" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G183" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E184" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G184" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E185" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G185" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E186" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="G186" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I182"/>
+  <autoFilter ref="A1:I186"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1193" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="311">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -280,6 +280,75 @@
     <t xml:space="preserve">SEPARADOR AR/OLEO ROTOR E PACK 4/5/6/10 HP        </t>
   </si>
   <si>
+    <t xml:space="preserve">020600017      </t>
+  </si>
+  <si>
+    <t>000001013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTERNADOR BOCH F000BL07R6 24                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020901199      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">REG. VOLT. ALT. IK5106                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020900815      </t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUSIVEL DE LAMINA 10A                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">030600053      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MINI FUSIVEL PERFIL BAIXO 10A                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600040      </t>
+  </si>
+  <si>
+    <t>000126254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CATALISADOR VIPAL VIPAFIX                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020601401      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANEL P/ MONTAGEM OR 325 T                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072600061      </t>
+  </si>
+  <si>
+    <t>000126027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COLA VIPAL VIPAFIX 1KG                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100144      </t>
+  </si>
+  <si>
+    <t>000002270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTA PVC VULCAFLEXCA-42291N°39                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100142      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTA PVC VULCAFLEXCA-42291N°37                    </t>
+  </si>
+  <si>
     <t>020202</t>
   </si>
   <si>
@@ -496,9 +565,36 @@
     <t xml:space="preserve">POLASEAL A4 UNITARIO                              </t>
   </si>
   <si>
+    <t xml:space="preserve">040300305      </t>
+  </si>
+  <si>
+    <t>000879559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITA CORRETIVA CIS TAPE 5MMX5,                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020800424      </t>
+  </si>
+  <si>
+    <t>000032767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO ATLASCOPCO 1613950300 ORIGINAL             </t>
+  </si>
+  <si>
     <t>020302</t>
   </si>
   <si>
+    <t xml:space="preserve">070601138      </t>
+  </si>
+  <si>
+    <t>004514924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INVERSOR WEG 15180353 CFW500G0180T4DB20C3H00G2    </t>
+  </si>
+  <si>
     <t xml:space="preserve">130600078      </t>
   </si>
   <si>
@@ -508,13 +604,16 @@
     <t xml:space="preserve">CALCA NR10 CLASSE2 CA-41.147 G AZUL ESCURO        </t>
   </si>
   <si>
-    <t xml:space="preserve">070601138      </t>
-  </si>
-  <si>
-    <t>004514924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INVERSOR WEG 15180353 CFW500G0180T4DB20C3H00G2    </t>
+    <t xml:space="preserve">130600092      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMISA NR10 CA-41.146 TAM G AZUL ESCURO           </t>
+  </si>
+  <si>
+    <t>001180913</t>
+  </si>
+  <si>
+    <t>000013550</t>
   </si>
   <si>
     <t>100106</t>
@@ -673,19 +772,169 @@
     <t xml:space="preserve">OLEO PETRONAS ATO 220 ISO VG 220                  </t>
   </si>
   <si>
-    <t xml:space="preserve">020400036      </t>
-  </si>
-  <si>
-    <t>000398227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLEO MOBIL 80W 20LT                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020400037      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLEO 10W40 MOBIL 20LT                             </t>
+    <t xml:space="preserve">040300154      </t>
+  </si>
+  <si>
+    <t>000000331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT 500HS CHICAGO PNEUMATIC CPS350-10             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300155      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT 1000HS CHICAGO PNEUMATIC CPS350-10            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201545      </t>
+  </si>
+  <si>
+    <t>000097291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 MOLA TRAS AXOX4144 MRB16206                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201546      </t>
+  </si>
+  <si>
+    <t>000097293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 MOLA TRAS AXOX4144 MRB16207                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201847      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MOLA DIANT AXOR4144 MRB18304                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200813      </t>
+  </si>
+  <si>
+    <t>000062617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JG TAMPA MERCEDES A 9433300956                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201494      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABRACADEIRA MERCEDES N1467                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040202237      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAFUSO MERCEDES N000000005729 M20X1,5X100       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090100042      </t>
+  </si>
+  <si>
+    <t>000002440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°36                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090100046      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°40                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090100048      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090500016      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROTETOR SOLAR 60FPS 120G                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090600013      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPUZ BALACLAVA CA-10979                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201694      </t>
+  </si>
+  <si>
+    <t>000062495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERRUPTOR MERCEDES A9585452107                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201861      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TUBULACAO MERCEDES A6954760801                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300126      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO MERCEDES A 0001421089                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040400059      </t>
+  </si>
+  <si>
+    <t>INTERRUPTOR DA TOMADA DE FORCA MERCEDES A958545030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201492      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABRAC. MERCEDES N000000002775                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">030200002      </t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>000011529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMARA DE AR 1200 R24 PEGASUS                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">090600033      </t>
+  </si>
+  <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>000024575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACACAO DE SEGURANCA XXG CA 11290                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201509      </t>
+  </si>
+  <si>
+    <t>000062680</t>
+  </si>
+  <si>
+    <t xml:space="preserve">POLIA MERCEDES A0005501933                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300018      </t>
+  </si>
+  <si>
+    <t>000048803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO MERCEDES A0004295795009                    </t>
   </si>
   <si>
     <t xml:space="preserve">040300116      </t>
@@ -695,138 +944,6 @@
   </si>
   <si>
     <t xml:space="preserve">FILTRO CAT 496-9841                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300154      </t>
-  </si>
-  <si>
-    <t>000000331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT 500HS CHICAGO PNEUMATIC CPS350-10             </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300155      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">KIT 1000HS CHICAGO PNEUMATIC CPS350-10            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201545      </t>
-  </si>
-  <si>
-    <t>000097291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 MOLA TRAS AXOX4144 MRB16206                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201546      </t>
-  </si>
-  <si>
-    <t>000097293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 MOLA TRAS AXOX4144 MRB16207                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201847      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 MOLA DIANT AXOR4144 MRB18304                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040200813      </t>
-  </si>
-  <si>
-    <t>000062617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JG TAMPA MERCEDES A 9433300956                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201494      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRACADEIRA MERCEDES N1467                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040202237      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PARAFUSO MERCEDES N000000005729 M20X1,5X100       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">090100042      </t>
-  </si>
-  <si>
-    <t>000002440</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°36                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">090100046      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°40                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">090100048      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">090500016      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROTETOR SOLAR 60FPS 120G                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">090600013      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPUZ BALACLAVA CA-10979                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201694      </t>
-  </si>
-  <si>
-    <t>000062495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">INTERRUPTOR MERCEDES A9585452107                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201861      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBULACAO MERCEDES A6954760801                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300126      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO MERCEDES A 0001421089                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040400059      </t>
-  </si>
-  <si>
-    <t>INTERRUPTOR DA TOMADA DE FORCA MERCEDES A958545030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201492      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRAC. MERCEDES N000000002775                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">030200002      </t>
-  </si>
-  <si>
-    <t>000011529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMARA DE AR 1200 R24 PEGASUS                     </t>
   </si>
 </sst>
 </file>
@@ -1224,18 +1341,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I149"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15.06" customWidth="1"/>
-    <col min="2" max="2" width="19.72" customWidth="1"/>
-    <col min="3" max="3" width="21.56" customWidth="1"/>
-    <col min="4" max="4" width="25.17" customWidth="1"/>
-    <col min="5" max="5" width="16.45" customWidth="1"/>
-    <col min="6" max="6" width="24.37" customWidth="1"/>
-    <col min="7" max="7" width="17.44" customWidth="1"/>
-    <col min="8" max="8" width="25.47" customWidth="1"/>
-    <col min="9" max="9" width="68.76" customWidth="1"/>
+    <col min="1" max="1" width="16.67" customWidth="1"/>
+    <col min="2" max="2" width="21.83" customWidth="1"/>
+    <col min="3" max="3" width="23.87" customWidth="1"/>
+    <col min="4" max="4" width="27.86" customWidth="1"/>
+    <col min="5" max="5" width="18.22" customWidth="1"/>
+    <col min="6" max="6" width="26.97" customWidth="1"/>
+    <col min="7" max="7" width="19.32" customWidth="1"/>
+    <col min="8" max="8" width="28.19" customWidth="1"/>
+    <col min="9" max="9" width="76.02" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2110,268 +2227,268 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="C31" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="G31" s="4">
+        <v>46314.5</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="G31" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G32" s="4">
+        <v>46314.5</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G32" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G33" s="4">
+        <v>46314.5</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="G33" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G34" s="4">
+        <v>46314.5</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G34" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G35" s="4">
-        <v>46310.5</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G36" s="4">
-        <v>46310.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G37" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G37" s="4">
-        <v>46310.5</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F38" s="2" t="s">
+      <c r="G38" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="G38" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G39" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>113</v>
@@ -2380,30 +2497,30 @@
         <v>11</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G40" s="4">
-        <v>46311.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>11</v>
@@ -2415,10 +2532,10 @@
         <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G41" s="4">
-        <v>46311.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>14</v>
@@ -2429,7 +2546,7 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>118</v>
@@ -2438,146 +2555,146 @@
         <v>11</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G42" s="4">
-        <v>46311.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="G43" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G44" s="4">
-        <v>46311.5</v>
+        <v>46310.5</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="G45" s="4">
-        <v>46311.5</v>
+        <v>46310.5</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G46" s="4">
-        <v>46311.5</v>
+        <v>46310.5</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>11</v>
@@ -2589,7 +2706,7 @@
         <v>58</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="G47" s="4">
         <v>46311.5</v>
@@ -2598,24 +2715,24 @@
         <v>14</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>132</v>
@@ -2627,24 +2744,24 @@
         <v>14</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>132</v>
@@ -2656,27 +2773,27 @@
         <v>14</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>137</v>
+        <v>12</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G50" s="4">
         <v>46311.5</v>
@@ -2685,28 +2802,28 @@
         <v>14</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="G51" s="4">
         <v>46311.5</v>
       </c>
@@ -2714,15 +2831,15 @@
         <v>14</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>11</v>
@@ -2734,7 +2851,7 @@
         <v>42</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G52" s="4">
         <v>46311.5</v>
@@ -2743,27 +2860,27 @@
         <v>14</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>29</v>
+        <v>146</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G53" s="4">
         <v>46311.5</v>
@@ -2772,27 +2889,27 @@
         <v>14</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="G54" s="4">
         <v>46311.5</v>
@@ -2801,56 +2918,56 @@
         <v>14</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>150</v>
+        <v>32</v>
       </c>
       <c r="F55" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I55" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G55" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="G56" s="4">
         <v>46311.5</v>
@@ -2859,30 +2976,30 @@
         <v>14</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>154</v>
+        <v>12</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>155</v>
       </c>
       <c r="G57" s="4">
-        <v>46314.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>14</v>
@@ -2893,7 +3010,7 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>157</v>
@@ -2902,16 +3019,16 @@
         <v>11</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>155</v>
       </c>
       <c r="G58" s="4">
-        <v>46314.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>14</v>
@@ -2922,7 +3039,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>159</v>
@@ -2931,27 +3048,27 @@
         <v>11</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>42</v>
+        <v>160</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>155</v>
       </c>
       <c r="G59" s="4">
-        <v>46314.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>162</v>
@@ -2960,317 +3077,317 @@
         <v>11</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F60" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G60" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I60" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="G60" s="4">
-        <v>46296.5</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="B61" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F61" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F61" s="2" t="s">
+      <c r="G61" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I61" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="G61" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G62" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="G62" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>173</v>
+        <v>20</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G63" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>20</v>
+        <v>173</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G64" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G65" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>20</v>
+        <v>177</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G66" s="4">
-        <v>46308.5</v>
+        <v>46314.5</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G67" s="4">
-        <v>46308.5</v>
+        <v>46314.5</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G68" s="4">
-        <v>46308.5</v>
+        <v>46314.5</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="G69" s="4">
-        <v>46308.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="B70" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="G70" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I70" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="G70" s="4">
-        <v>46308.5</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>191</v>
@@ -3285,155 +3402,155 @@
         <v>20</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="G71" s="4">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="G72" s="4">
-        <v>46308.5</v>
+        <v>46296.5</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C73" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>196</v>
-      </c>
       <c r="G73" s="4">
-        <v>46309.5</v>
+        <v>46296.5</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>198</v>
+        <v>25</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="G74" s="4">
-        <v>46309.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="B75" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="G75" s="4">
-        <v>46309.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B76" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C76" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="G76" s="4">
-        <v>46309.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>14</v>
@@ -3444,7 +3561,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>205</v>
@@ -3453,30 +3570,30 @@
         <v>11</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>42</v>
+        <v>206</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G77" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>11</v>
@@ -3488,126 +3605,126 @@
         <v>20</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G78" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B79" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="G79" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G80" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G81" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="G82" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>14</v>
@@ -3618,7 +3735,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>220</v>
@@ -3627,126 +3744,126 @@
         <v>11</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F83" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G83" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I83" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="G83" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G84" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I84" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="G84" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B85" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G85" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I85" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="G85" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="G86" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>229</v>
@@ -3758,44 +3875,44 @@
         <v>14</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G88" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>11</v>
@@ -3807,82 +3924,82 @@
         <v>20</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G89" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F90" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="G90" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I90" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="G90" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G91" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>181</v>
+        <v>241</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>11</v>
@@ -3894,68 +4011,68 @@
         <v>20</v>
       </c>
       <c r="F92" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G92" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I92" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="G92" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B93" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G93" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G93" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B94" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C94" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F94" s="2" t="s">
-        <v>242</v>
-      </c>
       <c r="G94" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>14</v>
@@ -3966,7 +4083,7 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>248</v>
@@ -3975,45 +4092,45 @@
         <v>11</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F95" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G95" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="G95" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B96" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="G96" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>14</v>
@@ -4024,7 +4141,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>253</v>
@@ -4039,65 +4156,65 @@
         <v>20</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G97" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>105</v>
+        <v>255</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B98" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="G98" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G99" s="4">
         <v>46311.5</v>
@@ -4106,15 +4223,15 @@
         <v>14</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>11</v>
@@ -4126,7 +4243,7 @@
         <v>20</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G100" s="4">
         <v>46311.5</v>
@@ -4135,27 +4252,27 @@
         <v>14</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G101" s="4">
         <v>46311.5</v>
@@ -4164,27 +4281,27 @@
         <v>14</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="G102" s="4">
         <v>46311.5</v>
@@ -4193,27 +4310,27 @@
         <v>14</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>265</v>
+        <v>214</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="G103" s="4">
         <v>46311.5</v>
@@ -4222,15 +4339,15 @@
         <v>14</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>266</v>
+        <v>215</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>11</v>
@@ -4242,7 +4359,7 @@
         <v>12</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="G104" s="4">
         <v>46311.5</v>
@@ -4251,44 +4368,44 @@
         <v>14</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="G105" s="4">
-        <v>46314.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>169</v>
+        <v>273</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>11</v>
@@ -4300,53 +4417,53 @@
         <v>20</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>170</v>
+        <v>274</v>
       </c>
       <c r="G106" s="4">
-        <v>46302.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>171</v>
+        <v>275</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>172</v>
+        <v>276</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>173</v>
+        <v>42</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>174</v>
+        <v>274</v>
       </c>
       <c r="G107" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>175</v>
+        <v>277</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>176</v>
+        <v>278</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>11</v>
@@ -4358,82 +4475,82 @@
         <v>20</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="G108" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="G109" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>180</v>
+        <v>280</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>181</v>
+        <v>281</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>177</v>
+        <v>274</v>
       </c>
       <c r="G110" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>182</v>
+        <v>282</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>183</v>
+        <v>283</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>11</v>
@@ -4445,82 +4562,82 @@
         <v>20</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="G111" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>184</v>
+        <v>285</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>185</v>
+        <v>286</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="G112" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>186</v>
+        <v>287</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>187</v>
+        <v>288</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="G113" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>188</v>
+        <v>289</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>189</v>
+        <v>290</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>11</v>
@@ -4532,181 +4649,181 @@
         <v>42</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="G114" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>190</v>
+        <v>291</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>191</v>
+        <v>292</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="G115" s="4">
-        <v>46308.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>192</v>
+        <v>293</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>193</v>
+        <v>294</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>42</v>
+        <v>146</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>42</v>
+        <v>295</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>177</v>
+        <v>296</v>
       </c>
       <c r="G116" s="4">
-        <v>46308.5</v>
+        <v>46314.5</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>194</v>
+        <v>297</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>195</v>
+        <v>298</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>42</v>
+        <v>299</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>42</v>
+        <v>299</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>196</v>
+        <v>300</v>
       </c>
       <c r="G117" s="4">
-        <v>46309.5</v>
+        <v>46314.5</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>197</v>
+        <v>301</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>198</v>
+        <v>302</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>196</v>
+        <v>303</v>
       </c>
       <c r="G118" s="4">
-        <v>46309.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>199</v>
+        <v>304</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>200</v>
+        <v>305</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="G119" s="4">
-        <v>46309.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>203</v>
+        <v>308</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>201</v>
+        <v>309</v>
       </c>
       <c r="G120" s="4">
         <v>46309.5</v>
@@ -4715,88 +4832,88 @@
         <v>14</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>204</v>
+        <v>310</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G121" s="4">
-        <v>46309.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B122" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G122" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I122" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="G122" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B123" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C123" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>206</v>
-      </c>
       <c r="G123" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>14</v>
@@ -4807,7 +4924,7 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>212</v>
@@ -4816,146 +4933,146 @@
         <v>11</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F124" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G124" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I124" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="G124" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B125" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G125" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I125" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="G125" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B126" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G126" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I126" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D126" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E126" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F126" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="G126" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="G127" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F128" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="G128" s="4">
+        <v>46308.5</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I128" s="2" t="s">
         <v>221</v>
-      </c>
-      <c r="G128" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>11</v>
@@ -4967,24 +5084,24 @@
         <v>42</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>226</v>
+        <v>210</v>
       </c>
       <c r="G129" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>11</v>
@@ -4996,140 +5113,140 @@
         <v>20</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="G130" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>229</v>
+        <v>210</v>
       </c>
       <c r="G131" s="4">
-        <v>46309.5</v>
+        <v>46308.5</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="G132" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>20</v>
+        <v>146</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="G133" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="G134" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>11</v>
@@ -5141,213 +5258,213 @@
         <v>29</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="G135" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G136" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>182</v>
+        <v>240</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F137" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G137" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I137" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="G137" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G138" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G139" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F140" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="G140" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I140" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="G140" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I140" s="2" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G141" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>14</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>105</v>
+        <v>252</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B142" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F142" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C142" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D142" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E142" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="G142" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>14</v>
@@ -5358,7 +5475,7 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B143" s="2" t="s">
         <v>256</v>
@@ -5367,16 +5484,16 @@
         <v>11</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="G143" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>14</v>
@@ -5387,7 +5504,7 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>258</v>
@@ -5416,7 +5533,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>261</v>
@@ -5431,7 +5548,7 @@
         <v>20</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G145" s="4">
         <v>46311.5</v>
@@ -5440,27 +5557,27 @@
         <v>14</v>
       </c>
       <c r="I145" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G146" s="4">
         <v>46311.5</v>
@@ -5469,27 +5586,27 @@
         <v>14</v>
       </c>
       <c r="I146" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="G147" s="4">
         <v>46311.5</v>
@@ -5498,28 +5615,28 @@
         <v>14</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E148" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F148" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C148" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D148" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E148" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F148" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="G148" s="4">
         <v>46311.5</v>
       </c>
@@ -5527,12 +5644,12 @@
         <v>14</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>269</v>
@@ -5541,26 +5658,490 @@
         <v>11</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>123</v>
+        <v>12</v>
       </c>
       <c r="F149" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G149" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I149" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G149" s="4">
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E150" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="G150" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G151" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G152" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G153" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G154" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G155" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E156" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G156" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E157" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G157" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E158" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G158" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E159" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G159" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E160" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="G160" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G161" s="4">
         <v>46314.5</v>
       </c>
-      <c r="H149" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I149" s="2" t="s">
-        <v>271</v>
+      <c r="H161" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="G162" s="4">
+        <v>46314.5</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G163" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="G164" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E165" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="G165" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>310</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I149"/>
+  <autoFilter ref="A1:I165"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="258">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -40,51 +40,435 @@
     <t xml:space="preserve">Descricao   </t>
   </si>
   <si>
+    <t>020102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130300035      </t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>340</t>
+  </si>
+  <si>
+    <t>000068267</t>
+  </si>
+  <si>
+    <t>SD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESPIRADOR PFF2 BRANCO CA-5657                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100059      </t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>000002306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCA VAQUETA M CA-45059                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130600093      </t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMISA NR10 CLASSE 2 CA-41.146 TAM GG AZUL ESCURO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130600028      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMISA NR10 CLASSE 2 CA-41.146 TAM M AZUL ESCURO  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130600076      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCA NR10 CLASSE2 CA-41.147 P AZUL ESCURO        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130600077      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCA NR10 CLASSE2 CA-41.147 M AZUL ESCURO        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130800061      </t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA VAQ PUNHO-20CM CA-20601 9                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130900042      </t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERNEIRA EM RASPA CA-21595                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010300010      </t>
+  </si>
+  <si>
+    <t>000004847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAS 141B P/ AR CONDICIONADO                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400363      </t>
+  </si>
+  <si>
+    <t>000021242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CORREIA 8PK 1345                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010500216      </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>000306368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAXA GADUS S3 V220 C 180KG                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130300015      </t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>000068157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO 3M 2097 P3                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130500001      </t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABAFADOR SEM HASTE CA-27971                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130800003      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA NITRILICA CA-43726                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130800103      </t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA TUNGSTENIO VOLK CA-47627                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020100033      </t>
+  </si>
+  <si>
+    <t>000013199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMPA CONTATOS SPRAY 300 ML                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020100126      </t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAZA THINNER SM 800 5LT                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300576      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCADOR INDUSTRIAL 60MR VERME                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">070700583      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA ROSQUEADA 5/8 X 1000                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">071100111      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOELHO ESGOTO 45 °X100 MM                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">071100209      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOELHO 45° 25MM                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072200043      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TINTA SPRAY 350ML VERDE FLUORECENTE               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072200126      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TINTA SPRAY PRETO 400ML BRILHANTE                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072600160      </t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIXA MASSA 150                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100129      </t>
+  </si>
+  <si>
+    <t>000164578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°38                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100130      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°39                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100131      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°40                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100132      </t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°41                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100133      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°42                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100134      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°43                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100160      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-34554 N°41                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100163      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-34554 N°44                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130800002      </t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA DE VAQUETA CA-20601 TAM 9                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130400001      </t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCULOS CINZA CA-11268                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020601021      </t>
+  </si>
+  <si>
+    <t>000002430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROLAMENTO SKF YAR 212-203-2F                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020605571      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROLAMENTO UC-206 FRM/SKF                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020606034      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROLAMENTO 33217 SKF                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010300005      </t>
+  </si>
+  <si>
+    <t>000004927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAS R-134 13,6KG EOS                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010500189      </t>
+  </si>
+  <si>
+    <t>000135458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES COMPLEAT 200LT LIQ ARREFREC                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020900003      </t>
+  </si>
+  <si>
+    <t>000002183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATERIA 150AH                                     </t>
+  </si>
+  <si>
+    <t>000002181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">020900083      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATERIA 90AH                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010200065      </t>
+  </si>
+  <si>
+    <t>000852213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 5458339                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">060500007      </t>
+  </si>
+  <si>
+    <t>000018303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RADIO DEP-450 VHF                                 </t>
+  </si>
+  <si>
+    <t>020202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180200041      </t>
+  </si>
+  <si>
+    <t>000002323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KIT FILTRO CHICAGO QD525 - 2901200520             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300458      </t>
+  </si>
+  <si>
+    <t>000880653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCA TEXTO AMARELO FABER CASTELL                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800264      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PILHA ALCALINA AAA 2X1                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800444      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITA DUPLA FACE 24MMX2M                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300026      </t>
+  </si>
+  <si>
+    <t>000880654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXTRATOR DE GRAMPO ESPATULA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040800792      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FITA CREPE 48MMX50MT                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300030      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAPISEIRA TECNOCIS 0,7M C 207                     </t>
+  </si>
+  <si>
     <t>020302</t>
   </si>
   <si>
     <t xml:space="preserve">070601138      </t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>004514924</t>
   </si>
   <si>
-    <t>SD1</t>
-  </si>
-  <si>
     <t xml:space="preserve">INVERSOR WEG 15180353 CFW500G0180T4DB20C3H00G2    </t>
   </si>
   <si>
-    <t xml:space="preserve">130600078      </t>
+    <t xml:space="preserve">020901055      </t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>000002215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CALCA NR10 CLASSE2 CA-41.147 G AZUL ESCURO        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">130600092      </t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMISA NR10 CA-41.146 TAM G AZUL ESCURO           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020901055      </t>
-  </si>
-  <si>
     <t>001180913</t>
   </si>
   <si>
@@ -115,9 +499,6 @@
     <t xml:space="preserve">180100894      </t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>000080991</t>
   </si>
   <si>
@@ -136,6 +517,45 @@
     <t xml:space="preserve">JUNTA EXPANSAO SERVFLEX 250X250 KB 1000           </t>
   </si>
   <si>
+    <t xml:space="preserve">040800821      </t>
+  </si>
+  <si>
+    <t>000004508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA P/ GAS GIULIANI ANELLO ST4B40BM 1.1/2"    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020608195      </t>
+  </si>
+  <si>
+    <t>000229652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RETENTOR BORRACHA NITRILICA SKF 70X110X12 HMS5 RG </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100128      </t>
+  </si>
+  <si>
+    <t>000002293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°37                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130200002      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACETE AZUL CA-498                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130200003      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPACETE BRANCO CA-498                            </t>
+  </si>
+  <si>
     <t>100106</t>
   </si>
   <si>
@@ -160,9 +580,6 @@
     <t xml:space="preserve">040201192      </t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t xml:space="preserve">JUNTA MERCEDES A4571310180                        </t>
   </si>
   <si>
@@ -211,9 +628,6 @@
     <t xml:space="preserve">040202237      </t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>000062617</t>
   </si>
   <si>
@@ -250,9 +664,6 @@
     <t xml:space="preserve">040201492      </t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t xml:space="preserve">ABRAC. MERCEDES N000000002775                     </t>
   </si>
   <si>
@@ -268,9 +679,6 @@
     <t xml:space="preserve">040300018      </t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>000048803</t>
   </si>
   <si>
@@ -326,6 +734,57 @@
   </si>
   <si>
     <t xml:space="preserve">OLEO CAT 7X-7858                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201829      </t>
+  </si>
+  <si>
+    <t>000044704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BUCHA A9473250050/R3366                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300022      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO MANN HU12110X                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">041400002      </t>
+  </si>
+  <si>
+    <t>000002182</t>
+  </si>
+  <si>
+    <t>000097387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300012      </t>
+  </si>
+  <si>
+    <t>000851428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 577-1435.000                           </t>
+  </si>
+  <si>
+    <t>000851429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201434      </t>
+  </si>
+  <si>
+    <t>000021172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACANETA MERCEDES A9417600559 LD EXTERNO          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201435      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACANETA MERCEDES A9417600459 LE EXTERNO          </t>
   </si>
 </sst>
 </file>
@@ -723,18 +1182,18 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="15.7" customWidth="1"/>
-    <col min="2" max="2" width="20.57" customWidth="1"/>
-    <col min="3" max="3" width="22.48" customWidth="1"/>
-    <col min="4" max="4" width="26.24" customWidth="1"/>
-    <col min="5" max="5" width="17.16" customWidth="1"/>
-    <col min="6" max="6" width="25.41" customWidth="1"/>
-    <col min="7" max="7" width="18.19" customWidth="1"/>
-    <col min="8" max="8" width="26.56" customWidth="1"/>
-    <col min="9" max="9" width="86.65" customWidth="1"/>
+    <col min="1" max="1" width="16.1" customWidth="1"/>
+    <col min="2" max="2" width="21.09" customWidth="1"/>
+    <col min="3" max="3" width="23.06" customWidth="1"/>
+    <col min="4" max="4" width="26.91" customWidth="1"/>
+    <col min="5" max="5" width="17.6" customWidth="1"/>
+    <col min="6" max="6" width="26.06" customWidth="1"/>
+    <col min="7" max="7" width="18.66" customWidth="1"/>
+    <col min="8" max="8" width="27.23" customWidth="1"/>
+    <col min="9" max="9" width="82.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -780,19 +1239,19 @@
         <v>12</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="4">
-        <v>46309.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -800,28 +1259,28 @@
         <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4">
-        <v>46296.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -829,28 +1288,28 @@
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4" s="4">
-        <v>46296.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -858,25 +1317,25 @@
         <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G5" s="4">
-        <v>46315.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>25</v>
@@ -893,22 +1352,22 @@
         <v>11</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" s="4">
-        <v>46315.5</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -916,28 +1375,28 @@
         <v>9</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="4">
-        <v>46316.5</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -945,28 +1404,28 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G8" s="4">
-        <v>46316.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -974,7 +1433,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>11</v>
@@ -986,16 +1445,16 @@
         <v>34</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="G9" s="4">
-        <v>46316.5</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1003,1308 +1462,3367 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G10" s="4">
-        <v>46316.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G11" s="4">
-        <v>46302.5</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G12" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="G13" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="E14" s="3" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="G14" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G19" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G19" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G20" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G21" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G22" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G23" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G24" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="G25" s="4">
-        <v>46315.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="G26" s="4">
-        <v>46315.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G27" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G28" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="G29" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="G30" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>85</v>
+        <v>47</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="G31" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="G32" s="4">
-        <v>46317.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="G33" s="4">
-        <v>46302.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>45</v>
+        <v>97</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="G34" s="4">
-        <v>46309.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>47</v>
+        <v>99</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="G35" s="4">
-        <v>46309.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>51</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="G36" s="4">
-        <v>46309.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>53</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>54</v>
+        <v>106</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="G37" s="4">
-        <v>46309.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="G38" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="G39" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>62</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="G40" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="G41" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>69</v>
+        <v>116</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="G42" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="G43" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>73</v>
+        <v>121</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>70</v>
+        <v>123</v>
       </c>
       <c r="G44" s="4">
-        <v>46311.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="G45" s="4">
-        <v>46311.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>78</v>
+        <v>125</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>70</v>
+        <v>126</v>
       </c>
       <c r="G46" s="4">
-        <v>46311.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>80</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="G47" s="4">
-        <v>46315.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>84</v>
+        <v>132</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="G48" s="4">
-        <v>46315.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>87</v>
+        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="G49" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>91</v>
+        <v>137</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="G50" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>94</v>
+        <v>140</v>
       </c>
       <c r="G51" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>95</v>
+        <v>141</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="G52" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>98</v>
+        <v>143</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="G53" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>41</v>
+        <v>146</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>102</v>
+        <v>43</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="G54" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G55" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G57" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G58" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G59" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="G60" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G61" s="4">
         <v>46317.5</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>104</v>
+      <c r="H61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G62" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G63" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G64" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G66" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G67" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G68" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G69" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G70" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G71" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G72" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G73" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G74" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G75" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G76" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G77" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G78" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G79" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G80" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G81" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G82" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G83" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G84" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G85" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G86" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G87" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G88" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G89" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G90" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G91" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G92" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G93" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G94" s="4">
+        <v>46319.5</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G95" s="4">
+        <v>46319.5</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G96" s="4">
+        <v>46302.5</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G97" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G98" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G99" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E100" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G100" s="4">
+        <v>46309.5</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G101" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G102" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G103" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G104" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G105" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G106" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E107" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G107" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E108" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G108" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E109" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G109" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E110" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G110" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E111" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G111" s="4">
+        <v>46315.5</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G112" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="G113" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G114" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G115" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G116" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="G117" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G118" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="G119" s="4">
+        <v>46317.5</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E120" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G120" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E121" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="G121" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G122" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G123" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G124" s="4">
+        <v>46319.5</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G125" s="4">
+        <v>46319.5</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>257</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I54"/>
+  <autoFilter ref="A1:I125"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="230">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -172,72 +172,60 @@
     <t xml:space="preserve">ABAFADOR SEM HASTE CA-27971                       </t>
   </si>
   <si>
-    <t xml:space="preserve">130800003      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA NITRILICA CA-43726                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">130800103      </t>
+    <t xml:space="preserve">020100033      </t>
+  </si>
+  <si>
+    <t>000013199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIMPA CONTATOS SPRAY 300 ML                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020100126      </t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAZA THINNER SM 800 5LT                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300576      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCADOR INDUSTRIAL 60MR VERME                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">070700583      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BARRA ROSQUEADA 5/8 X 1000                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">071100111      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOELHO ESGOTO 45 °X100 MM                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">071100209      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOELHO 45° 25MM                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072200043      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TINTA SPRAY 350ML VERDE FLUORECENTE               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">072200126      </t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
-    <t xml:space="preserve">LUVA TUNGSTENIO VOLK CA-47627                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020100033      </t>
-  </si>
-  <si>
-    <t>000013199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LIMPA CONTATOS SPRAY 300 ML                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020100126      </t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAZA THINNER SM 800 5LT                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300576      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARCADOR INDUSTRIAL 60MR VERME                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">070700583      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BARRA ROSQUEADA 5/8 X 1000                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">071100111      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOELHO ESGOTO 45 °X100 MM                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">071100209      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JOELHO 45° 25MM                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">072200043      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TINTA SPRAY 350ML VERDE FLUORECENTE               </t>
-  </si>
-  <si>
-    <t xml:space="preserve">072200126      </t>
-  </si>
-  <si>
     <t xml:space="preserve">TINTA SPRAY PRETO 400ML BRILHANTE                 </t>
   </si>
   <si>
@@ -313,15 +301,6 @@
     <t xml:space="preserve">LUVA DE VAQUETA CA-20601 TAM 9                    </t>
   </si>
   <si>
-    <t xml:space="preserve">130400001      </t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OCULOS CINZA CA-11268                             </t>
-  </si>
-  <si>
     <t xml:space="preserve">020601021      </t>
   </si>
   <si>
@@ -454,106 +433,43 @@
     <t>020302</t>
   </si>
   <si>
+    <t xml:space="preserve">020900502      </t>
+  </si>
+  <si>
+    <t>004514924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMI REMOTA CFW500-HMIR                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020900858      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CJ CABO IHM WEG CFW500-CCHMIR05M                  </t>
+  </si>
+  <si>
     <t xml:space="preserve">070601138      </t>
   </si>
   <si>
-    <t>004514924</t>
-  </si>
-  <si>
     <t xml:space="preserve">INVERSOR WEG 15180353 CFW500G0180T4DB20C3H00G2    </t>
   </si>
   <si>
-    <t xml:space="preserve">020901055      </t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>001180913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANTERNA CAB. RECARR. 7223A 5W                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020601223      </t>
-  </si>
-  <si>
-    <t>000013550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ROLAMENTO 6207-2RSC3                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">130900077      </t>
-  </si>
-  <si>
-    <t>155</t>
-  </si>
-  <si>
-    <t>000006786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BALACLAVA NINJA MONDIAL SAFETY PRETA | CA 44963   </t>
-  </si>
-  <si>
-    <t xml:space="preserve">180100894      </t>
-  </si>
-  <si>
-    <t>000080991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNTA EXPANSAO JEXP 2 150 KB1000                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">180100903      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNTA EXPANSAO SERVFLEX 200X200 KB1000            </t>
-  </si>
-  <si>
-    <t xml:space="preserve">180100904      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNTA EXPANSAO SERVFLEX 250X250 KB 1000           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040800821      </t>
-  </si>
-  <si>
-    <t>000004508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALVULA P/ GAS GIULIANI ANELLO ST4B40BM 1.1/2"    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020608195      </t>
-  </si>
-  <si>
-    <t>000229652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RETENTOR BORRACHA NITRILICA SKF 70X110X12 HMS5 RG </t>
-  </si>
-  <si>
-    <t xml:space="preserve">130100128      </t>
-  </si>
-  <si>
-    <t>000002293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°37                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">130200002      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPACETE AZUL CA-498                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">130200003      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAPACETE BRANCO CA-498                            </t>
+    <t xml:space="preserve">070602030      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MODULO COMUNICACAO CFW500-CRS4B                   </t>
+  </si>
+  <si>
+    <t>001033929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130800030      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUVA LATEX CA-15100 TAM 8                         </t>
+  </si>
+  <si>
+    <t>1.020</t>
   </si>
   <si>
     <t>100106</t>
@@ -1182,7 +1098,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I125"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16.1" customWidth="1"/>
@@ -1619,7 +1535,7 @@
         <v>31</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G15" s="4">
         <v>46318.5</v>
@@ -1628,7 +1544,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -1636,19 +1552,19 @@
         <v>9</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G16" s="4">
         <v>46318.5</v>
@@ -1657,7 +1573,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1665,7 +1581,7 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>11</v>
@@ -1677,7 +1593,7 @@
         <v>31</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G17" s="4">
         <v>46318.5</v>
@@ -1700,13 +1616,13 @@
         <v>11</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G18" s="4">
         <v>46318.5</v>
@@ -1715,7 +1631,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1723,19 +1639,19 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G19" s="4">
         <v>46318.5</v>
@@ -1744,7 +1660,7 @@
         <v>15</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1752,19 +1668,19 @@
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G20" s="4">
         <v>46318.5</v>
@@ -1773,7 +1689,7 @@
         <v>15</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1781,19 +1697,19 @@
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G21" s="4">
         <v>46318.5</v>
@@ -1802,7 +1718,7 @@
         <v>15</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1810,19 +1726,19 @@
         <v>9</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G22" s="4">
         <v>46318.5</v>
@@ -1845,13 +1761,13 @@
         <v>11</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G23" s="4">
         <v>46318.5</v>
@@ -1860,7 +1776,7 @@
         <v>15</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1868,19 +1784,19 @@
         <v>9</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="G24" s="4">
         <v>46318.5</v>
@@ -1889,7 +1805,7 @@
         <v>15</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1897,19 +1813,19 @@
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="G25" s="4">
         <v>46318.5</v>
@@ -1918,7 +1834,7 @@
         <v>15</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1926,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>11</v>
@@ -1938,7 +1854,7 @@
         <v>18</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G26" s="4">
         <v>46318.5</v>
@@ -1961,13 +1877,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G27" s="4">
         <v>46318.5</v>
@@ -1976,7 +1892,7 @@
         <v>15</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1984,19 +1900,19 @@
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G28" s="4">
         <v>46318.5</v>
@@ -2005,7 +1921,7 @@
         <v>15</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -2013,19 +1929,19 @@
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G29" s="4">
         <v>46318.5</v>
@@ -2048,13 +1964,13 @@
         <v>11</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G30" s="4">
         <v>46318.5</v>
@@ -2077,13 +1993,13 @@
         <v>11</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G31" s="4">
         <v>46318.5</v>
@@ -2106,13 +2022,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G32" s="4">
         <v>46318.5</v>
@@ -2121,7 +2037,7 @@
         <v>15</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -2129,19 +2045,19 @@
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="G33" s="4">
         <v>46318.5</v>
@@ -2150,7 +2066,7 @@
         <v>15</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -2158,19 +2074,19 @@
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="G34" s="4">
         <v>46318.5</v>
@@ -2179,7 +2095,7 @@
         <v>15</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
@@ -2187,19 +2103,19 @@
         <v>9</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>101</v>
+        <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="G35" s="4">
         <v>46318.5</v>
@@ -2251,13 +2167,13 @@
         <v>11</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="G37" s="4">
         <v>46318.5</v>
@@ -2266,7 +2182,7 @@
         <v>15</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2274,7 +2190,7 @@
         <v>9</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>11</v>
@@ -2286,7 +2202,7 @@
         <v>18</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="G38" s="4">
         <v>46318.5</v>
@@ -2295,7 +2211,7 @@
         <v>15</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2303,19 +2219,19 @@
         <v>9</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G39" s="4">
         <v>46318.5</v>
@@ -2324,7 +2240,7 @@
         <v>15</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2344,7 +2260,7 @@
         <v>43</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G40" s="4">
         <v>46318.5</v>
@@ -2353,7 +2269,7 @@
         <v>15</v>
       </c>
       <c r="I40" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
@@ -2361,28 +2277,28 @@
         <v>9</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="G41" s="4">
+        <v>46319.5</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="G41" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2390,28 +2306,28 @@
         <v>9</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>119</v>
       </c>
       <c r="G42" s="4">
-        <v>46318.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
@@ -2419,7 +2335,7 @@
         <v>9</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>11</v>
@@ -2434,18 +2350,18 @@
         <v>119</v>
       </c>
       <c r="G43" s="4">
-        <v>46318.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>122</v>
@@ -2454,16 +2370,16 @@
         <v>11</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G44" s="4">
-        <v>46319.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -2474,7 +2390,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>125</v>
@@ -2483,16 +2399,16 @@
         <v>11</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>126</v>
       </c>
       <c r="G45" s="4">
-        <v>46319.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -2503,51 +2419,51 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>9</v>
+        <v>121</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>126</v>
       </c>
       <c r="G46" s="4">
-        <v>46319.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G47" s="4">
         <v>46318.5</v>
@@ -2561,7 +2477,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>132</v>
@@ -2570,10 +2486,10 @@
         <v>11</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>133</v>
@@ -2590,7 +2506,7 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>135</v>
@@ -2599,10 +2515,10 @@
         <v>11</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>133</v>
@@ -2619,7 +2535,7 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>137</v>
@@ -2628,10 +2544,10 @@
         <v>11</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>133</v>
@@ -2648,94 +2564,94 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G51" s="4">
-        <v>46318.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G52" s="4">
-        <v>46318.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G53" s="4">
-        <v>46318.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>147</v>
@@ -2744,13 +2660,13 @@
         <v>11</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="G54" s="4">
         <v>46309.5</v>
@@ -2759,189 +2675,189 @@
         <v>15</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>150</v>
+        <v>82</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>151</v>
+        <v>22</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G55" s="4">
-        <v>46315.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>153</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G56" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G56" s="4">
-        <v>46315.5</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>157</v>
+        <v>10</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="G57" s="4">
-        <v>46316.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G58" s="4">
-        <v>46316.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G59" s="4">
-        <v>46316.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G60" s="4">
-        <v>46316.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>11</v>
@@ -2953,53 +2869,53 @@
         <v>18</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G61" s="4">
-        <v>46317.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G62" s="4">
-        <v>46317.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>11</v>
@@ -3011,239 +2927,239 @@
         <v>43</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="G63" s="4">
-        <v>46318.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G64" s="4">
-        <v>46318.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="F65" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G65" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I65" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="G65" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G66" s="4">
-        <v>46302.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G67" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I67" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G67" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G68" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G69" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="G70" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G71" s="4">
         <v>46311.5</v>
@@ -3252,160 +3168,160 @@
         <v>15</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G72" s="4">
-        <v>46311.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G73" s="4">
-        <v>46311.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G74" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G75" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G76" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>11</v>
@@ -3417,227 +3333,227 @@
         <v>43</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G77" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F78" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G78" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="G78" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G79" s="4">
-        <v>46311.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G80" s="4">
-        <v>46315.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G81" s="4">
-        <v>46315.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G82" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>226</v>
+        <v>111</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G83" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G84" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>11</v>
@@ -3649,82 +3565,82 @@
         <v>43</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="G85" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G86" s="4">
-        <v>46316.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="G87" s="4">
-        <v>46317.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>241</v>
+        <v>154</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
@@ -3736,111 +3652,111 @@
         <v>43</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>242</v>
+        <v>155</v>
       </c>
       <c r="G88" s="4">
-        <v>46317.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>243</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>242</v>
+        <v>158</v>
       </c>
       <c r="G89" s="4">
-        <v>46317.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>246</v>
+        <v>160</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>247</v>
+        <v>158</v>
       </c>
       <c r="G90" s="4">
-        <v>46318.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>118</v>
+        <v>161</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>248</v>
+        <v>163</v>
       </c>
       <c r="G91" s="4">
-        <v>46318.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>249</v>
+        <v>165</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>11</v>
@@ -3852,24 +3768,24 @@
         <v>43</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>250</v>
+        <v>166</v>
       </c>
       <c r="G92" s="4">
-        <v>46318.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>251</v>
+        <v>167</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>249</v>
+        <v>168</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>11</v>
@@ -3881,53 +3797,53 @@
         <v>43</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>252</v>
+        <v>169</v>
       </c>
       <c r="G93" s="4">
-        <v>46318.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>251</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>253</v>
+        <v>171</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="G94" s="4">
-        <v>46319.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>255</v>
+        <v>173</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>256</v>
+        <v>174</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>11</v>
@@ -3939,181 +3855,181 @@
         <v>18</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>254</v>
+        <v>172</v>
       </c>
       <c r="G95" s="4">
-        <v>46319.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>257</v>
+        <v>175</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G96" s="4">
-        <v>46302.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G97" s="4">
+        <v>46311.5</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="G97" s="4">
-        <v>46309.5</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="G98" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="G99" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="G100" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="G101" s="4">
         <v>46311.5</v>
@@ -4122,160 +4038,160 @@
         <v>15</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="G102" s="4">
-        <v>46311.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="G103" s="4">
-        <v>46311.5</v>
+        <v>46315.5</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="G104" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G105" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G106" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>11</v>
@@ -4287,227 +4203,227 @@
         <v>43</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="G107" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F108" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="G108" s="4">
+        <v>46316.5</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I108" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="G108" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="G109" s="4">
-        <v>46311.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="G110" s="4">
-        <v>46315.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G111" s="4">
-        <v>46315.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="G112" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>226</v>
+        <v>111</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>227</v>
+        <v>168</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G113" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="G114" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>11</v>
@@ -4519,310 +4435,78 @@
         <v>43</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="G115" s="4">
-        <v>46316.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="G116" s="4">
-        <v>46316.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>181</v>
+        <v>153</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>238</v>
+        <v>18</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="G117" s="4">
-        <v>46317.5</v>
+        <v>46319.5</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="C118" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E118" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G118" s="4">
-        <v>46317.5</v>
-      </c>
-      <c r="H118" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="E119" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F119" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="G119" s="4">
-        <v>46317.5</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I119" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A120" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D120" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E120" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="G120" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H120" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C121" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E121" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F121" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="G121" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D122" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E122" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G122" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H122" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E123" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F123" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="G123" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A124" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D124" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E124" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F124" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="G124" s="4">
-        <v>46319.5</v>
-      </c>
-      <c r="H124" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A125" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C125" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E125" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F125" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="G125" s="4">
-        <v>46319.5</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I125" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I125"/>
+  <autoFilter ref="A1:I117"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/dados/Lista de Produtos a Endereçar.xlsx
+++ b/dados/Lista de Produtos a Endereçar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="937" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="236">
   <si>
     <t xml:space="preserve">Filial      </t>
   </si>
@@ -130,15 +130,6 @@
     <t xml:space="preserve">GAS 141B P/ AR CONDICIONADO                       </t>
   </si>
   <si>
-    <t xml:space="preserve">020400363      </t>
-  </si>
-  <si>
-    <t>000021242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CORREIA 8PK 1345                                  </t>
-  </si>
-  <si>
     <t xml:space="preserve">010500216      </t>
   </si>
   <si>
@@ -268,12 +259,6 @@
     <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°41                     </t>
   </si>
   <si>
-    <t xml:space="preserve">130100133      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°42                     </t>
-  </si>
-  <si>
     <t xml:space="preserve">130100134      </t>
   </si>
   <si>
@@ -292,15 +277,6 @@
     <t xml:space="preserve">BOTINA MARLUVAS CA-34554 N°44                     </t>
   </si>
   <si>
-    <t xml:space="preserve">130800002      </t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUVA DE VAQUETA CA-20601 TAM 9                    </t>
-  </si>
-  <si>
     <t xml:space="preserve">020601021      </t>
   </si>
   <si>
@@ -367,13 +343,82 @@
     <t xml:space="preserve">FILTRO CAT 5458339                                </t>
   </si>
   <si>
-    <t xml:space="preserve">060500007      </t>
-  </si>
-  <si>
-    <t>000018303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RADIO DEP-450 VHF                                 </t>
+    <t xml:space="preserve">130100127      </t>
+  </si>
+  <si>
+    <t>000068345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°36                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100015      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTA DE BORRACHA N°42 CA-39347                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130100125      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOTINA MARLUVAS CA-42374 N°34                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020600037      </t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>000002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATERIA 100AH                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020800327      </t>
+  </si>
+  <si>
+    <t>000001026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO FLEETGUARD AF4201                          </t>
+  </si>
+  <si>
+    <t>000852557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">010200080      </t>
+  </si>
+  <si>
+    <t>000001033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO FLEETGUARD AF4207                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">130700068      </t>
+  </si>
+  <si>
+    <t>000024655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MACACAO DE SEG CA-11290 TAM G                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010500219      </t>
+  </si>
+  <si>
+    <t>000399285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO MOBIL ATF D/M PAIL 20LT                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">010700011      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO 600 XP 460 MOBIL 20LTS                       </t>
   </si>
   <si>
     <t>020202</t>
@@ -430,6 +475,15 @@
     <t xml:space="preserve">LAPISEIRA TECNOCIS 0,7M C 207                     </t>
   </si>
   <si>
+    <t xml:space="preserve">010500285      </t>
+  </si>
+  <si>
+    <t>000079349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLUIDO CHICAGO REFR CP46 19 LT - 1031401261       </t>
+  </si>
+  <si>
     <t>020302</t>
   </si>
   <si>
@@ -484,30 +538,6 @@
     <t xml:space="preserve">FILTRO CAT 439-5037                               </t>
   </si>
   <si>
-    <t xml:space="preserve">040200612      </t>
-  </si>
-  <si>
-    <t>000048733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMPRESSOR WABCO 8869025190193                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201192      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUNTA MERCEDES A4571310180                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040202167      </t>
-  </si>
-  <si>
-    <t>000048718</t>
-  </si>
-  <si>
-    <t>CILINDRO DE COMANDO DO GP CAMBIO RANGE A0022609563</t>
-  </si>
-  <si>
     <t xml:space="preserve">040300154      </t>
   </si>
   <si>
@@ -550,72 +580,15 @@
     <t xml:space="preserve">PARAFUSO MERCEDES N000000005729 M20X1,5X100       </t>
   </si>
   <si>
-    <t xml:space="preserve">040201694      </t>
+    <t xml:space="preserve">040400059      </t>
   </si>
   <si>
     <t>000062495</t>
   </si>
   <si>
-    <t xml:space="preserve">INTERRUPTOR MERCEDES A9585452107                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201861      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBULACAO MERCEDES A6954760801                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300126      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO MERCEDES A 0001421089                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040400059      </t>
-  </si>
-  <si>
     <t>INTERRUPTOR DA TOMADA DE FORCA MERCEDES A958545030</t>
   </si>
   <si>
-    <t xml:space="preserve">040201492      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRAC. MERCEDES N000000002775                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201509      </t>
-  </si>
-  <si>
-    <t>000062680</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLIA MERCEDES A0005501933                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040300018      </t>
-  </si>
-  <si>
-    <t>000048803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO MERCEDES A0004295795009                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040202258      </t>
-  </si>
-  <si>
-    <t>000062675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALAVANCA DE ACIONAMENTO DA EMBREAGEM A6552501513  </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040202259      </t>
-  </si>
-  <si>
-    <t>EIXO ALAVANCA ACIONAMENTO EMBREAGEM MB A6552540206</t>
-  </si>
-  <si>
     <t xml:space="preserve">040201573      </t>
   </si>
   <si>
@@ -625,33 +598,6 @@
     <t xml:space="preserve">PORCA MERCEDES N000000005738                      </t>
   </si>
   <si>
-    <t xml:space="preserve">040200813      </t>
-  </si>
-  <si>
-    <t>000062673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JG TAMPA MERCEDES A 9433300956                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201494      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ABRACADEIRA MERCEDES N1467                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">020400029      </t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>000851961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLEO CAT 7X-7858                                  </t>
-  </si>
-  <si>
     <t xml:space="preserve">040201829      </t>
   </si>
   <si>
@@ -661,46 +607,118 @@
     <t xml:space="preserve">BUCHA A9473250050/R3366                           </t>
   </si>
   <si>
-    <t xml:space="preserve">040300022      </t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO MANN HU12110X                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve">041400002      </t>
-  </si>
-  <si>
-    <t>000002182</t>
-  </si>
-  <si>
     <t>000097387</t>
   </si>
   <si>
-    <t xml:space="preserve">040300012      </t>
-  </si>
-  <si>
-    <t>000851428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FILTRO CAT 577-1435.000                           </t>
-  </si>
-  <si>
-    <t>000851429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">040201434      </t>
-  </si>
-  <si>
-    <t>000021172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACANETA MERCEDES A9417600559 LD EXTERNO          </t>
+    <t xml:space="preserve">040201693      </t>
+  </si>
+  <si>
+    <t>000062928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RETENTOR MERCEDES A0139977346                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201193      </t>
+  </si>
+  <si>
+    <t>000062934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MANGUEIRA MERCEDES A6179970082                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200687      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CILINDRO MERCEDES A9302600263                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201575      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PARAFUSO MERCEDES A0199906901                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201823      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOMBA MERCEDES A4574600280                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040202233      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">INTERRUPTOR COMANDO MERCEDES A0055453413          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300027      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO MERCEDES A0004301269                       </t>
   </si>
   <si>
     <t xml:space="preserve">040201435      </t>
   </si>
   <si>
+    <t>000062936</t>
+  </si>
+  <si>
     <t xml:space="preserve">MACANETA MERCEDES A9417600459 LE EXTERNO          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040201542      </t>
+  </si>
+  <si>
+    <t>000097551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 MOLA TRAS AXOX4144 MRB16203                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300109      </t>
+  </si>
+  <si>
+    <t>000852642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO CAT 256-7903                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve">020400019      </t>
+  </si>
+  <si>
+    <t>000399589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLEO MOBILUBE HD-A PLUS 80W90                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200746      </t>
+  </si>
+  <si>
+    <t>000048916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA MERCEDES A0024319215 6VIAS AXOR 4144      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040200799      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">VALVULA WABCO 4613152470                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300130      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO HYVA 081.02.117                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">040300131      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILTRO TANQUE HIDR BASC HYVA 14896992A            </t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1116,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16.1" customWidth="1"/>
@@ -1413,13 +1431,13 @@
         <v>11</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G11" s="4">
         <v>46318.5</v>
@@ -1428,7 +1446,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -1436,19 +1454,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G12" s="4">
         <v>46318.5</v>
@@ -1457,7 +1475,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -1465,19 +1483,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G13" s="4">
         <v>46318.5</v>
@@ -1500,13 +1518,13 @@
         <v>11</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="G14" s="4">
         <v>46318.5</v>
@@ -1529,13 +1547,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G15" s="4">
         <v>46318.5</v>
@@ -1558,13 +1576,13 @@
         <v>11</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G16" s="4">
         <v>46318.5</v>
@@ -1573,7 +1591,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -1581,19 +1599,19 @@
         <v>9</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G17" s="4">
         <v>46318.5</v>
@@ -1602,7 +1620,7 @@
         <v>15</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1610,19 +1628,19 @@
         <v>9</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G18" s="4">
         <v>46318.5</v>
@@ -1631,7 +1649,7 @@
         <v>15</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -1639,19 +1657,19 @@
         <v>9</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G19" s="4">
         <v>46318.5</v>
@@ -1660,7 +1678,7 @@
         <v>15</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -1668,19 +1686,19 @@
         <v>9</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G20" s="4">
         <v>46318.5</v>
@@ -1689,7 +1707,7 @@
         <v>15</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -1697,19 +1715,19 @@
         <v>9</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G21" s="4">
         <v>46318.5</v>
@@ -1738,7 +1756,7 @@
         <v>70</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G22" s="4">
         <v>46318.5</v>
@@ -1761,13 +1779,13 @@
         <v>11</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="G23" s="4">
         <v>46318.5</v>
@@ -1790,13 +1808,13 @@
         <v>11</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G24" s="4">
         <v>46318.5</v>
@@ -1805,7 +1823,7 @@
         <v>15</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
@@ -1813,19 +1831,19 @@
         <v>9</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G25" s="4">
         <v>46318.5</v>
@@ -1834,7 +1852,7 @@
         <v>15</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1842,19 +1860,19 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E26" s="3" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G26" s="4">
         <v>46318.5</v>
@@ -1877,13 +1895,13 @@
         <v>11</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G27" s="4">
         <v>46318.5</v>
@@ -1892,7 +1910,7 @@
         <v>15</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
@@ -1900,19 +1918,19 @@
         <v>9</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G28" s="4">
         <v>46318.5</v>
@@ -1921,7 +1939,7 @@
         <v>15</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -1929,19 +1947,19 @@
         <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G29" s="4">
         <v>46318.5</v>
@@ -1950,7 +1968,7 @@
         <v>15</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1958,19 +1976,19 @@
         <v>9</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>76</v>
       </c>
       <c r="G30" s="4">
         <v>46318.5</v>
@@ -1999,7 +2017,7 @@
         <v>18</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G31" s="4">
         <v>46318.5</v>
@@ -2022,13 +2040,13 @@
         <v>11</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="G32" s="4">
         <v>46318.5</v>
@@ -2037,7 +2055,7 @@
         <v>15</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -2045,19 +2063,19 @@
         <v>9</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="G33" s="4">
         <v>46318.5</v>
@@ -2066,7 +2084,7 @@
         <v>15</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -2074,19 +2092,19 @@
         <v>9</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="G34" s="4">
         <v>46318.5</v>
@@ -2115,7 +2133,7 @@
         <v>18</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G35" s="4">
         <v>46318.5</v>
@@ -2124,7 +2142,7 @@
         <v>15</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
@@ -2132,16 +2150,16 @@
         <v>9</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F36" s="2" t="s">
         <v>104</v>
@@ -2153,7 +2171,7 @@
         <v>15</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
@@ -2161,19 +2179,19 @@
         <v>9</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="G37" s="4">
         <v>46318.5</v>
@@ -2182,7 +2200,7 @@
         <v>15</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -2190,28 +2208,28 @@
         <v>9</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G38" s="4">
+        <v>46319.5</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G38" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -2219,7 +2237,7 @@
         <v>9</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>11</v>
@@ -2231,16 +2249,16 @@
         <v>18</v>
       </c>
       <c r="F39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G39" s="4">
+        <v>46322.5</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I39" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="G39" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
@@ -2254,16 +2272,16 @@
         <v>11</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G40" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -2283,22 +2301,22 @@
         <v>11</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F41" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G41" s="4">
+        <v>46322.5</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="G41" s="4">
-        <v>46319.5</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -2306,22 +2324,22 @@
         <v>9</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>119</v>
       </c>
       <c r="G42" s="4">
-        <v>46319.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -2335,62 +2353,62 @@
         <v>9</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G43" s="4">
-        <v>46319.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G44" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>124</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>125</v>
@@ -2399,16 +2417,16 @@
         <v>11</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>126</v>
       </c>
       <c r="G45" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -2419,7 +2437,7 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>128</v>
@@ -2428,100 +2446,100 @@
         <v>11</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="G46" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G47" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>121</v>
+        <v>9</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="G48" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G49" s="4">
         <v>46318.5</v>
@@ -2530,27 +2548,27 @@
         <v>15</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="G50" s="4">
         <v>46318.5</v>
@@ -2559,259 +2577,259 @@
         <v>15</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>141</v>
       </c>
       <c r="G51" s="4">
-        <v>46309.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>141</v>
       </c>
       <c r="G52" s="4">
-        <v>46309.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G53" s="4">
-        <v>46309.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="G54" s="4">
-        <v>46309.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>82</v>
+        <v>152</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G55" s="4">
-        <v>46311.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="G56" s="4">
-        <v>46311.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>10</v>
+        <v>158</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>152</v>
+        <v>18</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="G57" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>16</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G58" s="4">
-        <v>46302.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G59" s="4">
         <v>46309.5</v>
@@ -2820,27 +2838,27 @@
         <v>15</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>57</v>
+        <v>18</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="G60" s="4">
         <v>46309.5</v>
@@ -2849,85 +2867,85 @@
         <v>15</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="G61" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>164</v>
+        <v>81</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G62" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>168</v>
+        <v>10</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>43</v>
+        <v>170</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G63" s="4">
         <v>46311.5</v>
@@ -2936,85 +2954,85 @@
         <v>15</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>170</v>
+        <v>16</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G64" s="4">
-        <v>46311.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G65" s="4">
-        <v>46311.5</v>
+        <v>46309.5</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G66" s="4">
         <v>46311.5</v>
@@ -3023,27 +3041,27 @@
         <v>15</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G67" s="4">
         <v>46311.5</v>
@@ -3052,27 +3070,27 @@
         <v>15</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B68" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>180</v>
       </c>
       <c r="G68" s="4">
         <v>46311.5</v>
@@ -3081,27 +3099,27 @@
         <v>15</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G69" s="4">
         <v>46311.5</v>
@@ -3110,15 +3128,15 @@
         <v>15</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>11</v>
@@ -3127,10 +3145,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G70" s="4">
         <v>46311.5</v>
@@ -3139,244 +3157,244 @@
         <v>15</v>
       </c>
       <c r="I70" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>73</v>
+        <v>34</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="G71" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G72" s="4">
-        <v>46315.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="G73" s="4">
-        <v>46315.5</v>
+        <v>46318.5</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="G74" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G75" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G76" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G77" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G78" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>209</v>
@@ -3385,143 +3403,143 @@
         <v>11</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G79" s="4">
+        <v>46322.5</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I79" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G79" s="4">
-        <v>46317.5</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="G80" s="4">
-        <v>46317.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>73</v>
+        <v>18</v>
       </c>
       <c r="F81" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G81" s="4">
+        <v>46322.5</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I81" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="G81" s="4">
-        <v>46317.5</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G82" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>111</v>
+        <v>217</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>168</v>
+        <v>218</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F83" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G83" s="4">
+        <v>46322.5</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I83" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="G83" s="4">
-        <v>46318.5</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>221</v>
@@ -3530,16 +3548,16 @@
         <v>11</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>222</v>
       </c>
       <c r="G84" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -3550,196 +3568,196 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G85" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G86" s="4">
-        <v>46319.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B87" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F87" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>226</v>
-      </c>
       <c r="G87" s="4">
-        <v>46319.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>154</v>
+        <v>232</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>155</v>
+        <v>228</v>
       </c>
       <c r="G88" s="4">
-        <v>46302.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>156</v>
+        <v>233</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>157</v>
+        <v>234</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>158</v>
+        <v>228</v>
       </c>
       <c r="G89" s="4">
-        <v>46309.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>159</v>
+        <v>235</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G90" s="4">
-        <v>46309.5</v>
+        <v>46302.5</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="G91" s="4">
         <v>46309.5</v>
@@ -3748,56 +3766,56 @@
         <v>15</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="G92" s="4">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G93" s="4">
         <v>46311.5</v>
@@ -3806,27 +3824,27 @@
         <v>15</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G94" s="4">
         <v>46311.5</v>
@@ -3835,27 +3853,27 @@
         <v>15</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="G95" s="4">
         <v>46311.5</v>
@@ -3864,27 +3882,27 @@
         <v>15</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G96" s="4">
         <v>46311.5</v>
@@ -3893,218 +3911,218 @@
         <v>15</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="G97" s="4">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="G98" s="4">
-        <v>46311.5</v>
+        <v>46317.5</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F99" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G99" s="4">
+        <v>46318.5</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="G99" s="4">
-        <v>46311.5</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G100" s="4">
-        <v>46311.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>180</v>
+        <v>203</v>
       </c>
       <c r="G101" s="4">
-        <v>46311.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="G102" s="4">
-        <v>46315.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="G103" s="4">
-        <v>46315.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>11</v>
@@ -4116,397 +4134,339 @@
         <v>18</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G104" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G105" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G106" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G107" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="G108" s="4">
-        <v>46316.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="G109" s="4">
-        <v>46317.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G110" s="4">
-        <v>46317.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="G111" s="4">
-        <v>46317.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="G112" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>111</v>
+        <v>229</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="G113" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="G114" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>11</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="G115" s="4">
-        <v>46318.5</v>
+        <v>46322.5</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F116" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="G116" s="4">
-        <v>46319.5</v>
-      </c>
-      <c r="H116" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C117" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="G117" s="4">
-        <v>46319.5</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I117" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I117"/>
+  <autoFilter ref="A1:I115"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
